--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123617499</v>
+        <v>123617511</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>80734</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,25 +2195,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552214</v>
+        <v>552284</v>
       </c>
       <c r="R15" t="n">
-        <v>6992683</v>
+        <v>6992593</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617509</v>
+        <v>123617499</v>
       </c>
       <c r="B16" t="n">
-        <v>79393</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,25 +2297,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552284</v>
+        <v>552214</v>
       </c>
       <c r="R16" t="n">
-        <v>6992593</v>
+        <v>6992683</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617498</v>
+        <v>123617494</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>79399</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,25 +2399,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552204</v>
+        <v>552187</v>
       </c>
       <c r="R17" t="n">
-        <v>6992680</v>
+        <v>6992682</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617522</v>
+        <v>123617509</v>
       </c>
       <c r="B18" t="n">
-        <v>79364</v>
+        <v>79399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552067</v>
+        <v>552284</v>
       </c>
       <c r="R18" t="n">
-        <v>6992564</v>
+        <v>6992593</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617494</v>
+        <v>123617512</v>
       </c>
       <c r="B19" t="n">
-        <v>79393</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2603,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552187</v>
+        <v>552221</v>
       </c>
       <c r="R19" t="n">
-        <v>6992682</v>
+        <v>6992606</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617518</v>
+        <v>123617503</v>
       </c>
       <c r="B20" t="n">
-        <v>79856</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,25 +2705,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552178</v>
+        <v>552203</v>
       </c>
       <c r="R20" t="n">
-        <v>6992557</v>
+        <v>6992653</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2769,11 +2769,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2800,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617511</v>
+        <v>123617498</v>
       </c>
       <c r="B21" t="n">
-        <v>80732</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2812,25 +2807,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2840,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552284</v>
+        <v>552204</v>
       </c>
       <c r="R21" t="n">
-        <v>6992593</v>
+        <v>6992680</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2902,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123617497</v>
+        <v>123617500</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>92264</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,25 +2909,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2942,7 +2937,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552196</v>
+        <v>552262</v>
       </c>
       <c r="R22" t="n">
         <v>6992684</v>
@@ -3004,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617524</v>
+        <v>123617518</v>
       </c>
       <c r="B23" t="n">
-        <v>78420</v>
+        <v>79862</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3020,21 +3015,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3044,10 +3039,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552103</v>
+        <v>552178</v>
       </c>
       <c r="R23" t="n">
-        <v>6992492</v>
+        <v>6992557</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3080,6 +3075,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123617501</v>
+        <v>123617515</v>
       </c>
       <c r="B24" t="n">
-        <v>92275</v>
+        <v>90948</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3118,25 +3118,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552274</v>
+        <v>552174</v>
       </c>
       <c r="R24" t="n">
-        <v>6992684</v>
+        <v>6992595</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3182,11 +3182,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,10 +3208,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123617523</v>
+        <v>123617493</v>
       </c>
       <c r="B25" t="n">
-        <v>92247</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3225,25 +3220,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3253,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552103</v>
+        <v>552189</v>
       </c>
       <c r="R25" t="n">
-        <v>6992492</v>
+        <v>6992689</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3315,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123617514</v>
+        <v>123617510</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>78518</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3327,25 +3322,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3355,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552197</v>
+        <v>552284</v>
       </c>
       <c r="R26" t="n">
-        <v>6992592</v>
+        <v>6992593</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3417,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123617503</v>
+        <v>123617522</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>79370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3429,25 +3424,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552203</v>
+        <v>552067</v>
       </c>
       <c r="R27" t="n">
-        <v>6992653</v>
+        <v>6992564</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3519,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123617496</v>
+        <v>123617520</v>
       </c>
       <c r="B28" t="n">
-        <v>98379</v>
+        <v>78165</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3531,25 +3526,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3559,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552187</v>
+        <v>552067</v>
       </c>
       <c r="R28" t="n">
-        <v>6992682</v>
+        <v>6992564</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3621,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617506</v>
+        <v>123617504</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3661,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552200</v>
+        <v>552209</v>
       </c>
       <c r="R29" t="n">
-        <v>6992631</v>
+        <v>6992635</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3723,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123617500</v>
+        <v>123617497</v>
       </c>
       <c r="B30" t="n">
-        <v>92247</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3735,25 +3730,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,7 +3758,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552262</v>
+        <v>552196</v>
       </c>
       <c r="R30" t="n">
         <v>6992684</v>
@@ -3825,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123617510</v>
+        <v>123617492</v>
       </c>
       <c r="B31" t="n">
-        <v>78512</v>
+        <v>92264</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,25 +3832,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3865,10 +3860,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>552284</v>
+        <v>552193</v>
       </c>
       <c r="R31" t="n">
-        <v>6992593</v>
+        <v>6992693</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3927,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123617493</v>
+        <v>123617501</v>
       </c>
       <c r="B32" t="n">
-        <v>98379</v>
+        <v>92292</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,25 +3934,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552189</v>
+        <v>552274</v>
       </c>
       <c r="R32" t="n">
-        <v>6992689</v>
+        <v>6992684</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4003,6 +3998,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,10 +4029,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617504</v>
+        <v>123617513</v>
       </c>
       <c r="B33" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552209</v>
+        <v>552205</v>
       </c>
       <c r="R33" t="n">
-        <v>6992635</v>
+        <v>6992600</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4131,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617515</v>
+        <v>123617523</v>
       </c>
       <c r="B34" t="n">
-        <v>90931</v>
+        <v>92264</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4147,21 +4147,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552174</v>
+        <v>552103</v>
       </c>
       <c r="R34" t="n">
-        <v>6992595</v>
+        <v>6992492</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4236,7 +4236,7 @@
         <v>123617495</v>
       </c>
       <c r="B35" t="n">
-        <v>80732</v>
+        <v>80734</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617492</v>
+        <v>123617521</v>
       </c>
       <c r="B36" t="n">
-        <v>92247</v>
+        <v>77709</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4347,25 +4347,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552193</v>
+        <v>552067</v>
       </c>
       <c r="R36" t="n">
-        <v>6992693</v>
+        <v>6992564</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617513</v>
+        <v>123617491</v>
       </c>
       <c r="B37" t="n">
-        <v>98379</v>
+        <v>92264</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4449,25 +4449,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552205</v>
+        <v>552187</v>
       </c>
       <c r="R37" t="n">
-        <v>6992600</v>
+        <v>6992769</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617491</v>
+        <v>123617524</v>
       </c>
       <c r="B38" t="n">
-        <v>92247</v>
+        <v>78426</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4551,25 +4551,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552187</v>
+        <v>552103</v>
       </c>
       <c r="R38" t="n">
-        <v>6992769</v>
+        <v>6992492</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4641,10 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123617521</v>
+        <v>123617496</v>
       </c>
       <c r="B39" t="n">
-        <v>77703</v>
+        <v>98396</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4653,25 +4653,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>552067</v>
+        <v>552187</v>
       </c>
       <c r="R39" t="n">
-        <v>6992564</v>
+        <v>6992682</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123617512</v>
+        <v>123617506</v>
       </c>
       <c r="B40" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552221</v>
+        <v>552200</v>
       </c>
       <c r="R40" t="n">
-        <v>6992606</v>
+        <v>6992631</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123617520</v>
+        <v>123617514</v>
       </c>
       <c r="B41" t="n">
-        <v>78159</v>
+        <v>98396</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,25 +4857,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552067</v>
+        <v>552197</v>
       </c>
       <c r="R41" t="n">
-        <v>6992564</v>
+        <v>6992592</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617524</v>
+        <v>123617506</v>
       </c>
       <c r="B38" t="n">
-        <v>78426</v>
+        <v>98396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4551,25 +4551,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552103</v>
+        <v>552200</v>
       </c>
       <c r="R38" t="n">
-        <v>6992492</v>
+        <v>6992631</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123617506</v>
+        <v>123617524</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
+        <v>78426</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,25 +4755,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552200</v>
+        <v>552103</v>
       </c>
       <c r="R40" t="n">
-        <v>6992631</v>
+        <v>6992492</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617499</v>
+        <v>123617494</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>79399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,25 +2297,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552214</v>
+        <v>552187</v>
       </c>
       <c r="R16" t="n">
-        <v>6992683</v>
+        <v>6992682</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617494</v>
+        <v>123617509</v>
       </c>
       <c r="B17" t="n">
         <v>79399</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552187</v>
+        <v>552284</v>
       </c>
       <c r="R17" t="n">
-        <v>6992682</v>
+        <v>6992593</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617509</v>
+        <v>123617499</v>
       </c>
       <c r="B18" t="n">
-        <v>79399</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,25 +2501,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552284</v>
+        <v>552214</v>
       </c>
       <c r="R18" t="n">
-        <v>6992593</v>
+        <v>6992683</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -3616,7 +3616,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617504</v>
+        <v>123617497</v>
       </c>
       <c r="B29" t="n">
         <v>98396</v>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552209</v>
+        <v>552196</v>
       </c>
       <c r="R29" t="n">
-        <v>6992635</v>
+        <v>6992684</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123617497</v>
+        <v>123617504</v>
       </c>
       <c r="B30" t="n">
         <v>98396</v>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552196</v>
+        <v>552209</v>
       </c>
       <c r="R30" t="n">
-        <v>6992684</v>
+        <v>6992635</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617506</v>
+        <v>123617524</v>
       </c>
       <c r="B38" t="n">
-        <v>98396</v>
+        <v>78426</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4551,25 +4551,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552200</v>
+        <v>552103</v>
       </c>
       <c r="R38" t="n">
-        <v>6992631</v>
+        <v>6992492</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123617524</v>
+        <v>123617506</v>
       </c>
       <c r="B40" t="n">
-        <v>78426</v>
+        <v>98396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,25 +4755,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552103</v>
+        <v>552200</v>
       </c>
       <c r="R40" t="n">
-        <v>6992492</v>
+        <v>6992631</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617494</v>
+        <v>123617499</v>
       </c>
       <c r="B16" t="n">
-        <v>79399</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,25 +2297,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552187</v>
+        <v>552214</v>
       </c>
       <c r="R16" t="n">
-        <v>6992682</v>
+        <v>6992683</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617509</v>
+        <v>123617494</v>
       </c>
       <c r="B17" t="n">
         <v>79399</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552284</v>
+        <v>552187</v>
       </c>
       <c r="R17" t="n">
-        <v>6992593</v>
+        <v>6992682</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617499</v>
+        <v>123617509</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>79399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,25 +2501,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552214</v>
+        <v>552284</v>
       </c>
       <c r="R18" t="n">
-        <v>6992683</v>
+        <v>6992593</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617513</v>
+        <v>123617495</v>
       </c>
       <c r="B33" t="n">
-        <v>98396</v>
+        <v>80734</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4041,25 +4041,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552205</v>
+        <v>552187</v>
       </c>
       <c r="R33" t="n">
-        <v>6992600</v>
+        <v>6992682</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617495</v>
+        <v>123617513</v>
       </c>
       <c r="B35" t="n">
-        <v>80734</v>
+        <v>98396</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4245,25 +4245,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552187</v>
+        <v>552205</v>
       </c>
       <c r="R35" t="n">
-        <v>6992682</v>
+        <v>6992600</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617521</v>
+        <v>123617491</v>
       </c>
       <c r="B36" t="n">
-        <v>77709</v>
+        <v>92264</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4347,25 +4347,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552067</v>
+        <v>552187</v>
       </c>
       <c r="R36" t="n">
-        <v>6992564</v>
+        <v>6992769</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617491</v>
+        <v>123617521</v>
       </c>
       <c r="B37" t="n">
-        <v>92264</v>
+        <v>77709</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4449,25 +4449,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552187</v>
+        <v>552067</v>
       </c>
       <c r="R37" t="n">
-        <v>6992769</v>
+        <v>6992564</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123617511</v>
+        <v>123617501</v>
       </c>
       <c r="B15" t="n">
-        <v>80734</v>
+        <v>92297</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552284</v>
+        <v>552274</v>
       </c>
       <c r="R15" t="n">
-        <v>6992593</v>
+        <v>6992684</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,6 +2259,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617499</v>
+        <v>123617494</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>79404</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,25 +2302,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,10 +2330,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552214</v>
+        <v>552187</v>
       </c>
       <c r="R16" t="n">
-        <v>6992683</v>
+        <v>6992682</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2387,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617494</v>
+        <v>123617524</v>
       </c>
       <c r="B17" t="n">
-        <v>79399</v>
+        <v>78431</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,21 +2408,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2427,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552187</v>
+        <v>552103</v>
       </c>
       <c r="R17" t="n">
-        <v>6992682</v>
+        <v>6992492</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2492,7 +2497,7 @@
         <v>123617509</v>
       </c>
       <c r="B18" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2591,10 +2596,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617512</v>
+        <v>123617495</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>80739</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2608,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2636,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552221</v>
+        <v>552187</v>
       </c>
       <c r="R19" t="n">
-        <v>6992606</v>
+        <v>6992682</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617503</v>
+        <v>123617513</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552203</v>
+        <v>552205</v>
       </c>
       <c r="R20" t="n">
-        <v>6992653</v>
+        <v>6992600</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617498</v>
+        <v>123617496</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2835,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552204</v>
+        <v>552187</v>
       </c>
       <c r="R21" t="n">
-        <v>6992680</v>
+        <v>6992682</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123617500</v>
+        <v>123617520</v>
       </c>
       <c r="B22" t="n">
-        <v>92264</v>
+        <v>78170</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,25 +2914,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552262</v>
+        <v>552067</v>
       </c>
       <c r="R22" t="n">
-        <v>6992684</v>
+        <v>6992564</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617518</v>
+        <v>123617522</v>
       </c>
       <c r="B23" t="n">
-        <v>79862</v>
+        <v>79375</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,21 +3020,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3039,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552178</v>
+        <v>552067</v>
       </c>
       <c r="R23" t="n">
-        <v>6992557</v>
+        <v>6992564</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3075,11 +3080,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3109,7 +3109,7 @@
         <v>123617515</v>
       </c>
       <c r="B24" t="n">
-        <v>90948</v>
+        <v>90953</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>123617493</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123617510</v>
+        <v>123617521</v>
       </c>
       <c r="B26" t="n">
-        <v>78518</v>
+        <v>77714</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552284</v>
+        <v>552067</v>
       </c>
       <c r="R26" t="n">
-        <v>6992593</v>
+        <v>6992564</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123617522</v>
+        <v>123617518</v>
       </c>
       <c r="B27" t="n">
-        <v>79370</v>
+        <v>79867</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552067</v>
+        <v>552178</v>
       </c>
       <c r="R27" t="n">
-        <v>6992564</v>
+        <v>6992557</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3488,6 +3488,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,10 +3519,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123617520</v>
+        <v>123617499</v>
       </c>
       <c r="B28" t="n">
-        <v>78165</v>
+        <v>98502</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,25 +3531,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552067</v>
+        <v>552214</v>
       </c>
       <c r="R28" t="n">
-        <v>6992564</v>
+        <v>6992683</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3616,10 +3621,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617497</v>
+        <v>123617498</v>
       </c>
       <c r="B29" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3656,10 +3661,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552196</v>
+        <v>552204</v>
       </c>
       <c r="R29" t="n">
-        <v>6992684</v>
+        <v>6992680</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3718,10 +3723,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123617504</v>
+        <v>123617497</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3758,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552209</v>
+        <v>552196</v>
       </c>
       <c r="R30" t="n">
-        <v>6992635</v>
+        <v>6992684</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3823,7 +3828,7 @@
         <v>123617492</v>
       </c>
       <c r="B31" t="n">
-        <v>92264</v>
+        <v>92269</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3922,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123617501</v>
+        <v>123617511</v>
       </c>
       <c r="B32" t="n">
-        <v>92292</v>
+        <v>80739</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,21 +3943,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>1049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3962,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552274</v>
+        <v>552284</v>
       </c>
       <c r="R32" t="n">
-        <v>6992684</v>
+        <v>6992593</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3998,11 +4003,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,10 +4029,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617495</v>
+        <v>123617491</v>
       </c>
       <c r="B33" t="n">
-        <v>80734</v>
+        <v>92269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4041,25 +4041,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4072,7 +4072,7 @@
         <v>552187</v>
       </c>
       <c r="R33" t="n">
-        <v>6992682</v>
+        <v>6992769</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4131,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617523</v>
+        <v>123617504</v>
       </c>
       <c r="B34" t="n">
-        <v>92264</v>
+        <v>98502</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4143,25 +4143,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552103</v>
+        <v>552209</v>
       </c>
       <c r="R34" t="n">
-        <v>6992492</v>
+        <v>6992635</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617513</v>
+        <v>123617500</v>
       </c>
       <c r="B35" t="n">
-        <v>98396</v>
+        <v>92269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4245,25 +4245,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552205</v>
+        <v>552262</v>
       </c>
       <c r="R35" t="n">
-        <v>6992600</v>
+        <v>6992684</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617491</v>
+        <v>123617510</v>
       </c>
       <c r="B36" t="n">
-        <v>92264</v>
+        <v>78523</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4347,25 +4347,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552187</v>
+        <v>552284</v>
       </c>
       <c r="R36" t="n">
-        <v>6992769</v>
+        <v>6992593</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617521</v>
+        <v>123617523</v>
       </c>
       <c r="B37" t="n">
-        <v>77709</v>
+        <v>92269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4449,25 +4449,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552067</v>
+        <v>552103</v>
       </c>
       <c r="R37" t="n">
-        <v>6992564</v>
+        <v>6992492</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617524</v>
+        <v>123617514</v>
       </c>
       <c r="B38" t="n">
-        <v>78426</v>
+        <v>98502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4551,25 +4551,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552103</v>
+        <v>552197</v>
       </c>
       <c r="R38" t="n">
-        <v>6992492</v>
+        <v>6992592</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4641,10 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123617496</v>
+        <v>123617503</v>
       </c>
       <c r="B39" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>552187</v>
+        <v>552203</v>
       </c>
       <c r="R39" t="n">
-        <v>6992682</v>
+        <v>6992653</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4746,7 +4746,7 @@
         <v>123617506</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123617514</v>
+        <v>123617512</v>
       </c>
       <c r="B41" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552197</v>
+        <v>552221</v>
       </c>
       <c r="R41" t="n">
-        <v>6992592</v>
+        <v>6992606</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2186,7 +2186,7 @@
         <v>123617501</v>
       </c>
       <c r="B15" t="n">
-        <v>92297</v>
+        <v>92299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617494</v>
+        <v>123617491</v>
       </c>
       <c r="B16" t="n">
-        <v>79404</v>
+        <v>92271</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,25 +2302,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
         <v>552187</v>
       </c>
       <c r="R16" t="n">
-        <v>6992682</v>
+        <v>6992769</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617524</v>
+        <v>123617506</v>
       </c>
       <c r="B17" t="n">
-        <v>78431</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,25 +2404,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552103</v>
+        <v>552200</v>
       </c>
       <c r="R17" t="n">
-        <v>6992492</v>
+        <v>6992631</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617509</v>
+        <v>123617524</v>
       </c>
       <c r="B18" t="n">
-        <v>79404</v>
+        <v>78433</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,21 +2510,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552284</v>
+        <v>552103</v>
       </c>
       <c r="R18" t="n">
-        <v>6992593</v>
+        <v>6992492</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2596,10 +2596,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617495</v>
+        <v>123617522</v>
       </c>
       <c r="B19" t="n">
-        <v>80739</v>
+        <v>79377</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552187</v>
+        <v>552067</v>
       </c>
       <c r="R19" t="n">
-        <v>6992682</v>
+        <v>6992564</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617513</v>
+        <v>123617521</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>77716</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2710,25 +2710,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552205</v>
+        <v>552067</v>
       </c>
       <c r="R20" t="n">
-        <v>6992600</v>
+        <v>6992564</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617496</v>
+        <v>123617494</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>79406</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2812,25 +2812,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123617520</v>
+        <v>123617509</v>
       </c>
       <c r="B22" t="n">
-        <v>78170</v>
+        <v>79406</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552067</v>
+        <v>552284</v>
       </c>
       <c r="R22" t="n">
-        <v>6992564</v>
+        <v>6992593</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617522</v>
+        <v>123617512</v>
       </c>
       <c r="B23" t="n">
-        <v>79375</v>
+        <v>98504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,25 +3016,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552067</v>
+        <v>552221</v>
       </c>
       <c r="R23" t="n">
-        <v>6992564</v>
+        <v>6992606</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123617515</v>
+        <v>123617518</v>
       </c>
       <c r="B24" t="n">
-        <v>90953</v>
+        <v>79869</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3118,25 +3118,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552174</v>
+        <v>552178</v>
       </c>
       <c r="R24" t="n">
-        <v>6992595</v>
+        <v>6992557</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3182,6 +3182,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3208,10 +3213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123617493</v>
+        <v>123617492</v>
       </c>
       <c r="B25" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3220,25 +3225,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3248,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552189</v>
+        <v>552193</v>
       </c>
       <c r="R25" t="n">
-        <v>6992689</v>
+        <v>6992693</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3310,10 +3315,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123617521</v>
+        <v>123617520</v>
       </c>
       <c r="B26" t="n">
-        <v>77714</v>
+        <v>78172</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,21 +3331,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123617518</v>
+        <v>123617513</v>
       </c>
       <c r="B27" t="n">
-        <v>79867</v>
+        <v>98504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3424,25 +3429,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552178</v>
+        <v>552205</v>
       </c>
       <c r="R27" t="n">
-        <v>6992557</v>
+        <v>6992600</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3488,11 +3493,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3519,10 +3519,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123617499</v>
+        <v>123617511</v>
       </c>
       <c r="B28" t="n">
-        <v>98502</v>
+        <v>80741</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552214</v>
+        <v>552284</v>
       </c>
       <c r="R28" t="n">
-        <v>6992683</v>
+        <v>6992593</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3621,10 +3621,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617498</v>
+        <v>123617500</v>
       </c>
       <c r="B29" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3633,25 +3633,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552204</v>
+        <v>552262</v>
       </c>
       <c r="R29" t="n">
-        <v>6992680</v>
+        <v>6992684</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3723,10 +3723,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123617497</v>
+        <v>123617496</v>
       </c>
       <c r="B30" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552196</v>
+        <v>552187</v>
       </c>
       <c r="R30" t="n">
-        <v>6992684</v>
+        <v>6992682</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123617492</v>
+        <v>123617495</v>
       </c>
       <c r="B31" t="n">
-        <v>92269</v>
+        <v>80741</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,25 +3837,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>552193</v>
+        <v>552187</v>
       </c>
       <c r="R31" t="n">
-        <v>6992693</v>
+        <v>6992682</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3927,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123617511</v>
+        <v>123617499</v>
       </c>
       <c r="B32" t="n">
-        <v>80739</v>
+        <v>98504</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,25 +3939,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552284</v>
+        <v>552214</v>
       </c>
       <c r="R32" t="n">
-        <v>6992593</v>
+        <v>6992683</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617491</v>
+        <v>123617514</v>
       </c>
       <c r="B33" t="n">
-        <v>92269</v>
+        <v>98504</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4041,25 +4041,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552187</v>
+        <v>552197</v>
       </c>
       <c r="R33" t="n">
-        <v>6992769</v>
+        <v>6992592</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4131,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617504</v>
+        <v>123617498</v>
       </c>
       <c r="B34" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552209</v>
+        <v>552204</v>
       </c>
       <c r="R34" t="n">
-        <v>6992635</v>
+        <v>6992680</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617500</v>
+        <v>123617510</v>
       </c>
       <c r="B35" t="n">
-        <v>92269</v>
+        <v>78525</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4245,25 +4245,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552262</v>
+        <v>552284</v>
       </c>
       <c r="R35" t="n">
-        <v>6992684</v>
+        <v>6992593</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617510</v>
+        <v>123617497</v>
       </c>
       <c r="B36" t="n">
-        <v>78523</v>
+        <v>98504</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4347,25 +4347,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552284</v>
+        <v>552196</v>
       </c>
       <c r="R36" t="n">
-        <v>6992593</v>
+        <v>6992684</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617523</v>
+        <v>123617504</v>
       </c>
       <c r="B37" t="n">
-        <v>92269</v>
+        <v>98504</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4449,25 +4449,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552103</v>
+        <v>552209</v>
       </c>
       <c r="R37" t="n">
-        <v>6992492</v>
+        <v>6992635</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617514</v>
+        <v>123617493</v>
       </c>
       <c r="B38" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552197</v>
+        <v>552189</v>
       </c>
       <c r="R38" t="n">
-        <v>6992592</v>
+        <v>6992689</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4641,10 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123617503</v>
+        <v>123617523</v>
       </c>
       <c r="B39" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4653,25 +4653,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>552203</v>
+        <v>552103</v>
       </c>
       <c r="R39" t="n">
-        <v>6992653</v>
+        <v>6992492</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123617506</v>
+        <v>123617515</v>
       </c>
       <c r="B40" t="n">
-        <v>98502</v>
+        <v>90955</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,25 +4755,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552200</v>
+        <v>552174</v>
       </c>
       <c r="R40" t="n">
-        <v>6992631</v>
+        <v>6992595</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123617512</v>
+        <v>123617503</v>
       </c>
       <c r="B41" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552221</v>
+        <v>552203</v>
       </c>
       <c r="R41" t="n">
-        <v>6992606</v>
+        <v>6992653</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -3004,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617512</v>
+        <v>123617518</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>79869</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,25 +3016,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552221</v>
+        <v>552178</v>
       </c>
       <c r="R23" t="n">
-        <v>6992606</v>
+        <v>6992557</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3080,6 +3080,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123617518</v>
+        <v>123617512</v>
       </c>
       <c r="B24" t="n">
-        <v>79869</v>
+        <v>98504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3118,25 +3123,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3146,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552178</v>
+        <v>552221</v>
       </c>
       <c r="R24" t="n">
-        <v>6992557</v>
+        <v>6992606</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3182,11 +3187,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -3519,10 +3519,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123617511</v>
+        <v>123617500</v>
       </c>
       <c r="B28" t="n">
-        <v>80741</v>
+        <v>92271</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552284</v>
+        <v>552262</v>
       </c>
       <c r="R28" t="n">
-        <v>6992593</v>
+        <v>6992684</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3621,10 +3621,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617500</v>
+        <v>123617511</v>
       </c>
       <c r="B29" t="n">
-        <v>92271</v>
+        <v>80741</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3633,25 +3633,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552262</v>
+        <v>552284</v>
       </c>
       <c r="R29" t="n">
-        <v>6992684</v>
+        <v>6992593</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123617501</v>
+        <v>123617498</v>
       </c>
       <c r="B15" t="n">
-        <v>92299</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,25 +2195,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552274</v>
+        <v>552204</v>
       </c>
       <c r="R15" t="n">
-        <v>6992684</v>
+        <v>6992680</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,11 +2259,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617491</v>
+        <v>123617521</v>
       </c>
       <c r="B16" t="n">
-        <v>92271</v>
+        <v>77716</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,25 +2297,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2330,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552187</v>
+        <v>552067</v>
       </c>
       <c r="R16" t="n">
-        <v>6992769</v>
+        <v>6992564</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2395,7 +2390,7 @@
         <v>123617506</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2494,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617524</v>
+        <v>123617511</v>
       </c>
       <c r="B18" t="n">
-        <v>78433</v>
+        <v>80741</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,21 +2505,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2534,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552103</v>
+        <v>552284</v>
       </c>
       <c r="R18" t="n">
-        <v>6992492</v>
+        <v>6992593</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2596,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617522</v>
+        <v>123617513</v>
       </c>
       <c r="B19" t="n">
-        <v>79377</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2608,25 +2603,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2636,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552067</v>
+        <v>552205</v>
       </c>
       <c r="R19" t="n">
-        <v>6992564</v>
+        <v>6992600</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2698,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617521</v>
+        <v>123617510</v>
       </c>
       <c r="B20" t="n">
-        <v>77716</v>
+        <v>78525</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2714,21 +2709,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2738,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552067</v>
+        <v>552284</v>
       </c>
       <c r="R20" t="n">
-        <v>6992564</v>
+        <v>6992593</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2800,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617494</v>
+        <v>123617515</v>
       </c>
       <c r="B21" t="n">
-        <v>79406</v>
+        <v>90955</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2812,25 +2807,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2840,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552187</v>
+        <v>552174</v>
       </c>
       <c r="R21" t="n">
-        <v>6992682</v>
+        <v>6992595</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2902,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123617509</v>
+        <v>123617500</v>
       </c>
       <c r="B22" t="n">
-        <v>79406</v>
+        <v>92271</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,25 +2909,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552284</v>
+        <v>552262</v>
       </c>
       <c r="R22" t="n">
-        <v>6992593</v>
+        <v>6992684</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617518</v>
+        <v>123617522</v>
       </c>
       <c r="B23" t="n">
-        <v>79869</v>
+        <v>79377</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3020,21 +3015,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3044,10 +3039,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552178</v>
+        <v>552067</v>
       </c>
       <c r="R23" t="n">
-        <v>6992557</v>
+        <v>6992564</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3080,11 +3075,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3111,10 +3101,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123617512</v>
+        <v>123617523</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>92271</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3123,25 +3113,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3151,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552221</v>
+        <v>552103</v>
       </c>
       <c r="R24" t="n">
-        <v>6992606</v>
+        <v>6992492</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3315,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123617520</v>
+        <v>123617496</v>
       </c>
       <c r="B26" t="n">
-        <v>78172</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3327,25 +3317,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3355,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552067</v>
+        <v>552187</v>
       </c>
       <c r="R26" t="n">
-        <v>6992564</v>
+        <v>6992682</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3417,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123617513</v>
+        <v>123617493</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3457,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552205</v>
+        <v>552189</v>
       </c>
       <c r="R27" t="n">
-        <v>6992600</v>
+        <v>6992689</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3519,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123617500</v>
+        <v>123617495</v>
       </c>
       <c r="B28" t="n">
-        <v>92271</v>
+        <v>80741</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3531,25 +3521,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3559,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552262</v>
+        <v>552187</v>
       </c>
       <c r="R28" t="n">
-        <v>6992684</v>
+        <v>6992682</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3621,10 +3611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617511</v>
+        <v>123617494</v>
       </c>
       <c r="B29" t="n">
-        <v>80741</v>
+        <v>79406</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3637,21 +3627,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3661,10 +3651,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552284</v>
+        <v>552187</v>
       </c>
       <c r="R29" t="n">
-        <v>6992593</v>
+        <v>6992682</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3723,10 +3713,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123617496</v>
+        <v>123617509</v>
       </c>
       <c r="B30" t="n">
-        <v>98504</v>
+        <v>79406</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3735,25 +3725,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3753,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552187</v>
+        <v>552284</v>
       </c>
       <c r="R30" t="n">
-        <v>6992682</v>
+        <v>6992593</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3825,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123617495</v>
+        <v>123617524</v>
       </c>
       <c r="B31" t="n">
-        <v>80741</v>
+        <v>78433</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3841,21 +3831,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3865,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>552187</v>
+        <v>552103</v>
       </c>
       <c r="R31" t="n">
-        <v>6992682</v>
+        <v>6992492</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3927,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123617499</v>
+        <v>123617518</v>
       </c>
       <c r="B32" t="n">
-        <v>98504</v>
+        <v>79869</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,25 +3929,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552214</v>
+        <v>552178</v>
       </c>
       <c r="R32" t="n">
-        <v>6992683</v>
+        <v>6992557</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4003,6 +3993,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617514</v>
+        <v>123617504</v>
       </c>
       <c r="B33" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4069,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552197</v>
+        <v>552209</v>
       </c>
       <c r="R33" t="n">
-        <v>6992592</v>
+        <v>6992635</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4131,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617498</v>
+        <v>123617514</v>
       </c>
       <c r="B34" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4171,10 +4166,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552204</v>
+        <v>552197</v>
       </c>
       <c r="R34" t="n">
-        <v>6992680</v>
+        <v>6992592</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4233,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617510</v>
+        <v>123617520</v>
       </c>
       <c r="B35" t="n">
-        <v>78525</v>
+        <v>78172</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4249,21 +4244,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4273,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552284</v>
+        <v>552067</v>
       </c>
       <c r="R35" t="n">
-        <v>6992593</v>
+        <v>6992564</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4338,7 +4333,7 @@
         <v>123617497</v>
       </c>
       <c r="B36" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4437,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617504</v>
+        <v>123617501</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>92299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4449,25 +4444,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4477,10 +4472,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552209</v>
+        <v>552274</v>
       </c>
       <c r="R37" t="n">
-        <v>6992635</v>
+        <v>6992684</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4513,6 +4508,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617493</v>
+        <v>123617491</v>
       </c>
       <c r="B38" t="n">
-        <v>98504</v>
+        <v>92271</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4551,25 +4551,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552189</v>
+        <v>552187</v>
       </c>
       <c r="R38" t="n">
-        <v>6992689</v>
+        <v>6992769</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4641,10 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123617523</v>
+        <v>123617499</v>
       </c>
       <c r="B39" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4653,25 +4653,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>552103</v>
+        <v>552214</v>
       </c>
       <c r="R39" t="n">
-        <v>6992492</v>
+        <v>6992683</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123617515</v>
+        <v>123617512</v>
       </c>
       <c r="B40" t="n">
-        <v>90955</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,25 +4755,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552174</v>
+        <v>552221</v>
       </c>
       <c r="R40" t="n">
-        <v>6992595</v>
+        <v>6992606</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4848,7 +4848,7 @@
         <v>123617503</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617511</v>
+        <v>123617510</v>
       </c>
       <c r="B18" t="n">
-        <v>80741</v>
+        <v>78525</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617513</v>
+        <v>123617511</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>80741</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2603,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552205</v>
+        <v>552284</v>
       </c>
       <c r="R19" t="n">
-        <v>6992600</v>
+        <v>6992593</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617510</v>
+        <v>123617515</v>
       </c>
       <c r="B20" t="n">
-        <v>78525</v>
+        <v>90955</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,25 +2705,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552284</v>
+        <v>552174</v>
       </c>
       <c r="R20" t="n">
-        <v>6992593</v>
+        <v>6992595</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617515</v>
+        <v>123617513</v>
       </c>
       <c r="B21" t="n">
-        <v>90955</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552174</v>
+        <v>552205</v>
       </c>
       <c r="R21" t="n">
-        <v>6992595</v>
+        <v>6992600</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3917,10 +3917,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123617518</v>
+        <v>123617504</v>
       </c>
       <c r="B32" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3929,25 +3929,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552178</v>
+        <v>552209</v>
       </c>
       <c r="R32" t="n">
-        <v>6992557</v>
+        <v>6992635</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3993,11 +3993,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4024,10 +4019,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617504</v>
+        <v>123617518</v>
       </c>
       <c r="B33" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4036,25 +4031,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4064,10 +4059,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552209</v>
+        <v>552178</v>
       </c>
       <c r="R33" t="n">
-        <v>6992635</v>
+        <v>6992557</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4100,6 +4095,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617520</v>
+        <v>123617497</v>
       </c>
       <c r="B35" t="n">
-        <v>78172</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,25 +4240,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552067</v>
+        <v>552196</v>
       </c>
       <c r="R35" t="n">
-        <v>6992564</v>
+        <v>6992684</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617497</v>
+        <v>123617520</v>
       </c>
       <c r="B36" t="n">
-        <v>98079</v>
+        <v>78172</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4342,25 +4342,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552196</v>
+        <v>552067</v>
       </c>
       <c r="R36" t="n">
-        <v>6992684</v>
+        <v>6992564</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123617498</v>
+        <v>123617493</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552204</v>
+        <v>552189</v>
       </c>
       <c r="R15" t="n">
-        <v>6992680</v>
+        <v>6992689</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617521</v>
+        <v>123617500</v>
       </c>
       <c r="B16" t="n">
-        <v>77716</v>
+        <v>92271</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,25 +2297,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552067</v>
+        <v>552262</v>
       </c>
       <c r="R16" t="n">
-        <v>6992564</v>
+        <v>6992684</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617506</v>
+        <v>123617503</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552200</v>
+        <v>552203</v>
       </c>
       <c r="R17" t="n">
-        <v>6992631</v>
+        <v>6992653</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617510</v>
+        <v>123617491</v>
       </c>
       <c r="B18" t="n">
-        <v>78525</v>
+        <v>92271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,25 +2501,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552284</v>
+        <v>552187</v>
       </c>
       <c r="R18" t="n">
-        <v>6992593</v>
+        <v>6992769</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617511</v>
+        <v>123617513</v>
       </c>
       <c r="B19" t="n">
-        <v>80741</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2603,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552284</v>
+        <v>552205</v>
       </c>
       <c r="R19" t="n">
-        <v>6992593</v>
+        <v>6992600</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617515</v>
+        <v>123617518</v>
       </c>
       <c r="B20" t="n">
-        <v>90955</v>
+        <v>79869</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,25 +2705,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552174</v>
+        <v>552178</v>
       </c>
       <c r="R20" t="n">
-        <v>6992595</v>
+        <v>6992557</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2769,6 +2769,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2795,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617513</v>
+        <v>123617510</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>78525</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,25 +2812,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552205</v>
+        <v>552284</v>
       </c>
       <c r="R21" t="n">
-        <v>6992600</v>
+        <v>6992593</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123617500</v>
+        <v>123617511</v>
       </c>
       <c r="B22" t="n">
-        <v>92271</v>
+        <v>80741</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,25 +2914,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552262</v>
+        <v>552284</v>
       </c>
       <c r="R22" t="n">
-        <v>6992684</v>
+        <v>6992593</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617522</v>
+        <v>123617512</v>
       </c>
       <c r="B23" t="n">
-        <v>79377</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3011,25 +3016,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3039,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552067</v>
+        <v>552221</v>
       </c>
       <c r="R23" t="n">
-        <v>6992564</v>
+        <v>6992606</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3101,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123617523</v>
+        <v>123617496</v>
       </c>
       <c r="B24" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,25 +3118,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3146,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552103</v>
+        <v>552187</v>
       </c>
       <c r="R24" t="n">
-        <v>6992492</v>
+        <v>6992682</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3203,10 +3208,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123617492</v>
+        <v>123617499</v>
       </c>
       <c r="B25" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,25 +3220,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3243,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552193</v>
+        <v>552214</v>
       </c>
       <c r="R25" t="n">
-        <v>6992693</v>
+        <v>6992683</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3305,7 +3310,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123617496</v>
+        <v>123617514</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3345,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552187</v>
+        <v>552197</v>
       </c>
       <c r="R26" t="n">
-        <v>6992682</v>
+        <v>6992592</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3407,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123617493</v>
+        <v>123617501</v>
       </c>
       <c r="B27" t="n">
-        <v>98079</v>
+        <v>92299</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,25 +3424,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3447,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552189</v>
+        <v>552274</v>
       </c>
       <c r="R27" t="n">
-        <v>6992689</v>
+        <v>6992684</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3483,6 +3488,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3509,10 +3519,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123617495</v>
+        <v>123617520</v>
       </c>
       <c r="B28" t="n">
-        <v>80741</v>
+        <v>78172</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3525,21 +3535,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552187</v>
+        <v>552067</v>
       </c>
       <c r="R28" t="n">
-        <v>6992682</v>
+        <v>6992564</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3611,10 +3621,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617494</v>
+        <v>123617497</v>
       </c>
       <c r="B29" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3623,25 +3633,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3651,10 +3661,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552187</v>
+        <v>552196</v>
       </c>
       <c r="R29" t="n">
-        <v>6992682</v>
+        <v>6992684</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3713,10 +3723,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123617509</v>
+        <v>123617492</v>
       </c>
       <c r="B30" t="n">
-        <v>79406</v>
+        <v>92271</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3725,25 +3735,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3753,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552284</v>
+        <v>552193</v>
       </c>
       <c r="R30" t="n">
-        <v>6992593</v>
+        <v>6992693</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3815,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123617524</v>
+        <v>123617522</v>
       </c>
       <c r="B31" t="n">
-        <v>78433</v>
+        <v>79377</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,21 +3841,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3855,10 +3865,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>552103</v>
+        <v>552067</v>
       </c>
       <c r="R31" t="n">
-        <v>6992492</v>
+        <v>6992564</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3917,7 +3927,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123617504</v>
+        <v>123617506</v>
       </c>
       <c r="B32" t="n">
         <v>98079</v>
@@ -3957,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552209</v>
+        <v>552200</v>
       </c>
       <c r="R32" t="n">
-        <v>6992635</v>
+        <v>6992631</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4019,10 +4029,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617518</v>
+        <v>123617521</v>
       </c>
       <c r="B33" t="n">
-        <v>79869</v>
+        <v>77716</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4035,21 +4045,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4059,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552178</v>
+        <v>552067</v>
       </c>
       <c r="R33" t="n">
-        <v>6992557</v>
+        <v>6992564</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4095,11 +4105,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4126,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617514</v>
+        <v>123617524</v>
       </c>
       <c r="B34" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4138,25 +4143,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4166,10 +4171,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552197</v>
+        <v>552103</v>
       </c>
       <c r="R34" t="n">
-        <v>6992592</v>
+        <v>6992492</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4228,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617497</v>
+        <v>123617523</v>
       </c>
       <c r="B35" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,25 +4245,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4268,10 +4273,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552196</v>
+        <v>552103</v>
       </c>
       <c r="R35" t="n">
-        <v>6992684</v>
+        <v>6992492</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4330,10 +4335,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617520</v>
+        <v>123617515</v>
       </c>
       <c r="B36" t="n">
-        <v>78172</v>
+        <v>90955</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4342,25 +4347,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552067</v>
+        <v>552174</v>
       </c>
       <c r="R36" t="n">
-        <v>6992564</v>
+        <v>6992595</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4432,10 +4437,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617501</v>
+        <v>123617495</v>
       </c>
       <c r="B37" t="n">
-        <v>92299</v>
+        <v>80741</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4448,21 +4453,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>1049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4472,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552274</v>
+        <v>552187</v>
       </c>
       <c r="R37" t="n">
-        <v>6992684</v>
+        <v>6992682</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4508,11 +4513,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4539,10 +4539,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617491</v>
+        <v>123617494</v>
       </c>
       <c r="B38" t="n">
-        <v>92271</v>
+        <v>79406</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4551,25 +4551,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4582,7 +4582,7 @@
         <v>552187</v>
       </c>
       <c r="R38" t="n">
-        <v>6992769</v>
+        <v>6992682</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123617499</v>
+        <v>123617498</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>552214</v>
+        <v>552204</v>
       </c>
       <c r="R39" t="n">
-        <v>6992683</v>
+        <v>6992680</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123617512</v>
+        <v>123617504</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552221</v>
+        <v>552209</v>
       </c>
       <c r="R40" t="n">
-        <v>6992606</v>
+        <v>6992635</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123617503</v>
+        <v>123617509</v>
       </c>
       <c r="B41" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,25 +4857,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552203</v>
+        <v>552284</v>
       </c>
       <c r="R41" t="n">
-        <v>6992653</v>
+        <v>6992593</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123617493</v>
+        <v>123617497</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552189</v>
+        <v>552196</v>
       </c>
       <c r="R15" t="n">
-        <v>6992689</v>
+        <v>6992684</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617500</v>
+        <v>123617521</v>
       </c>
       <c r="B16" t="n">
-        <v>92271</v>
+        <v>77716</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,25 +2297,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552262</v>
+        <v>552067</v>
       </c>
       <c r="R16" t="n">
-        <v>6992684</v>
+        <v>6992564</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617503</v>
+        <v>123617500</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,25 +2399,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552203</v>
+        <v>552262</v>
       </c>
       <c r="R17" t="n">
-        <v>6992653</v>
+        <v>6992684</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2489,7 +2489,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617491</v>
+        <v>123617523</v>
       </c>
       <c r="B18" t="n">
         <v>92271</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552187</v>
+        <v>552103</v>
       </c>
       <c r="R18" t="n">
-        <v>6992769</v>
+        <v>6992492</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617513</v>
+        <v>123617491</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2603,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552205</v>
+        <v>552187</v>
       </c>
       <c r="R19" t="n">
-        <v>6992600</v>
+        <v>6992769</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617518</v>
+        <v>123617520</v>
       </c>
       <c r="B20" t="n">
-        <v>79869</v>
+        <v>78172</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552178</v>
+        <v>552067</v>
       </c>
       <c r="R20" t="n">
-        <v>6992557</v>
+        <v>6992564</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2769,11 +2769,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3004,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617512</v>
+        <v>123617492</v>
       </c>
       <c r="B23" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,25 +3011,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3044,10 +3039,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552221</v>
+        <v>552193</v>
       </c>
       <c r="R23" t="n">
-        <v>6992606</v>
+        <v>6992693</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3106,7 +3101,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123617496</v>
+        <v>123617514</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -3146,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552187</v>
+        <v>552197</v>
       </c>
       <c r="R24" t="n">
-        <v>6992682</v>
+        <v>6992592</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3208,7 +3203,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123617499</v>
+        <v>123617506</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3248,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552214</v>
+        <v>552200</v>
       </c>
       <c r="R25" t="n">
-        <v>6992683</v>
+        <v>6992631</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3310,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123617514</v>
+        <v>123617494</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3322,25 +3317,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552197</v>
+        <v>552187</v>
       </c>
       <c r="R26" t="n">
-        <v>6992592</v>
+        <v>6992682</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3412,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123617501</v>
+        <v>123617495</v>
       </c>
       <c r="B27" t="n">
-        <v>92299</v>
+        <v>80741</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3428,21 +3423,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552274</v>
+        <v>552187</v>
       </c>
       <c r="R27" t="n">
-        <v>6992684</v>
+        <v>6992682</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3488,11 +3483,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3519,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123617520</v>
+        <v>123617504</v>
       </c>
       <c r="B28" t="n">
-        <v>78172</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3531,25 +3521,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3559,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552067</v>
+        <v>552209</v>
       </c>
       <c r="R28" t="n">
-        <v>6992564</v>
+        <v>6992635</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3621,10 +3611,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617497</v>
+        <v>123617509</v>
       </c>
       <c r="B29" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3633,25 +3623,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3661,10 +3651,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552196</v>
+        <v>552284</v>
       </c>
       <c r="R29" t="n">
-        <v>6992684</v>
+        <v>6992593</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3723,10 +3713,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123617492</v>
+        <v>123617522</v>
       </c>
       <c r="B30" t="n">
-        <v>92271</v>
+        <v>79377</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3735,25 +3725,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3753,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552193</v>
+        <v>552067</v>
       </c>
       <c r="R30" t="n">
-        <v>6992693</v>
+        <v>6992564</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3825,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123617522</v>
+        <v>123617503</v>
       </c>
       <c r="B31" t="n">
-        <v>79377</v>
+        <v>98079</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,25 +3827,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3865,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>552067</v>
+        <v>552203</v>
       </c>
       <c r="R31" t="n">
-        <v>6992564</v>
+        <v>6992653</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3927,7 +3917,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123617506</v>
+        <v>123617496</v>
       </c>
       <c r="B32" t="n">
         <v>98079</v>
@@ -3967,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552200</v>
+        <v>552187</v>
       </c>
       <c r="R32" t="n">
-        <v>6992631</v>
+        <v>6992682</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4029,10 +4019,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617521</v>
+        <v>123617513</v>
       </c>
       <c r="B33" t="n">
-        <v>77716</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4041,25 +4031,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4069,10 +4059,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552067</v>
+        <v>552205</v>
       </c>
       <c r="R33" t="n">
-        <v>6992564</v>
+        <v>6992600</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4131,10 +4121,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617524</v>
+        <v>123617501</v>
       </c>
       <c r="B34" t="n">
-        <v>78433</v>
+        <v>92299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4147,21 +4137,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4171,10 +4161,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552103</v>
+        <v>552274</v>
       </c>
       <c r="R34" t="n">
-        <v>6992492</v>
+        <v>6992684</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4207,6 +4197,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4233,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617523</v>
+        <v>123617524</v>
       </c>
       <c r="B35" t="n">
-        <v>92271</v>
+        <v>78433</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4245,25 +4240,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4335,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617515</v>
+        <v>123617499</v>
       </c>
       <c r="B36" t="n">
-        <v>90955</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4347,25 +4342,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4375,10 +4370,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552174</v>
+        <v>552214</v>
       </c>
       <c r="R36" t="n">
-        <v>6992595</v>
+        <v>6992683</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4437,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617495</v>
+        <v>123617512</v>
       </c>
       <c r="B37" t="n">
-        <v>80741</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4449,25 +4444,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4477,10 +4472,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552187</v>
+        <v>552221</v>
       </c>
       <c r="R37" t="n">
-        <v>6992682</v>
+        <v>6992606</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4539,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617494</v>
+        <v>123617498</v>
       </c>
       <c r="B38" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4551,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4579,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552187</v>
+        <v>552204</v>
       </c>
       <c r="R38" t="n">
-        <v>6992682</v>
+        <v>6992680</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4641,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123617498</v>
+        <v>123617515</v>
       </c>
       <c r="B39" t="n">
-        <v>98079</v>
+        <v>90955</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4653,25 +4648,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4681,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>552204</v>
+        <v>552174</v>
       </c>
       <c r="R39" t="n">
-        <v>6992680</v>
+        <v>6992595</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4743,7 +4738,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123617504</v>
+        <v>123617493</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -4783,10 +4778,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552209</v>
+        <v>552189</v>
       </c>
       <c r="R40" t="n">
-        <v>6992635</v>
+        <v>6992689</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4845,10 +4840,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123617509</v>
+        <v>123617518</v>
       </c>
       <c r="B41" t="n">
-        <v>79406</v>
+        <v>79869</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4861,21 +4856,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4885,10 +4880,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552284</v>
+        <v>552178</v>
       </c>
       <c r="R41" t="n">
-        <v>6992593</v>
+        <v>6992557</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4921,6 +4916,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123617497</v>
+        <v>123617504</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552196</v>
+        <v>552209</v>
       </c>
       <c r="R15" t="n">
-        <v>6992684</v>
+        <v>6992635</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617521</v>
+        <v>123617492</v>
       </c>
       <c r="B16" t="n">
-        <v>77716</v>
+        <v>92271</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,25 +2297,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552067</v>
+        <v>552193</v>
       </c>
       <c r="R16" t="n">
-        <v>6992564</v>
+        <v>6992693</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617523</v>
+        <v>123617520</v>
       </c>
       <c r="B18" t="n">
-        <v>92271</v>
+        <v>78172</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,25 +2501,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552103</v>
+        <v>552067</v>
       </c>
       <c r="R18" t="n">
-        <v>6992492</v>
+        <v>6992564</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617491</v>
+        <v>123617512</v>
       </c>
       <c r="B19" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2603,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552187</v>
+        <v>552221</v>
       </c>
       <c r="R19" t="n">
-        <v>6992769</v>
+        <v>6992606</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617520</v>
+        <v>123617497</v>
       </c>
       <c r="B20" t="n">
-        <v>78172</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,25 +2705,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552067</v>
+        <v>552196</v>
       </c>
       <c r="R20" t="n">
-        <v>6992564</v>
+        <v>6992684</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617510</v>
+        <v>123617491</v>
       </c>
       <c r="B21" t="n">
-        <v>78525</v>
+        <v>92271</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552284</v>
+        <v>552187</v>
       </c>
       <c r="R21" t="n">
-        <v>6992593</v>
+        <v>6992769</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123617511</v>
+        <v>123617493</v>
       </c>
       <c r="B22" t="n">
-        <v>80741</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,25 +2909,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552284</v>
+        <v>552189</v>
       </c>
       <c r="R22" t="n">
-        <v>6992593</v>
+        <v>6992689</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617492</v>
+        <v>123617515</v>
       </c>
       <c r="B23" t="n">
-        <v>92271</v>
+        <v>90955</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3015,21 +3015,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552193</v>
+        <v>552174</v>
       </c>
       <c r="R23" t="n">
-        <v>6992693</v>
+        <v>6992595</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123617514</v>
+        <v>123617510</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
+        <v>78525</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,25 +3113,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552197</v>
+        <v>552284</v>
       </c>
       <c r="R24" t="n">
-        <v>6992592</v>
+        <v>6992593</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123617506</v>
+        <v>123617496</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552200</v>
+        <v>552187</v>
       </c>
       <c r="R25" t="n">
-        <v>6992631</v>
+        <v>6992682</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123617494</v>
+        <v>123617498</v>
       </c>
       <c r="B26" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3317,25 +3317,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552187</v>
+        <v>552204</v>
       </c>
       <c r="R26" t="n">
-        <v>6992682</v>
+        <v>6992680</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123617495</v>
+        <v>123617523</v>
       </c>
       <c r="B27" t="n">
-        <v>80741</v>
+        <v>92271</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,25 +3419,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552187</v>
+        <v>552103</v>
       </c>
       <c r="R27" t="n">
-        <v>6992682</v>
+        <v>6992492</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123617504</v>
+        <v>123617501</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
+        <v>92299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,25 +3521,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552209</v>
+        <v>552274</v>
       </c>
       <c r="R28" t="n">
-        <v>6992635</v>
+        <v>6992684</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3585,6 +3585,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3611,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617509</v>
+        <v>123617506</v>
       </c>
       <c r="B29" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3623,25 +3628,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3651,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552284</v>
+        <v>552200</v>
       </c>
       <c r="R29" t="n">
-        <v>6992593</v>
+        <v>6992631</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3713,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123617522</v>
+        <v>123617524</v>
       </c>
       <c r="B30" t="n">
-        <v>79377</v>
+        <v>78433</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3729,21 +3734,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3753,10 +3758,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552067</v>
+        <v>552103</v>
       </c>
       <c r="R30" t="n">
-        <v>6992564</v>
+        <v>6992492</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3815,7 +3820,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123617503</v>
+        <v>123617499</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -3855,10 +3860,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>552203</v>
+        <v>552214</v>
       </c>
       <c r="R31" t="n">
-        <v>6992653</v>
+        <v>6992683</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3917,7 +3922,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123617496</v>
+        <v>123617513</v>
       </c>
       <c r="B32" t="n">
         <v>98079</v>
@@ -3957,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552187</v>
+        <v>552205</v>
       </c>
       <c r="R32" t="n">
-        <v>6992682</v>
+        <v>6992600</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4019,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617513</v>
+        <v>123617495</v>
       </c>
       <c r="B33" t="n">
-        <v>98079</v>
+        <v>80741</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4031,25 +4036,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4059,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552205</v>
+        <v>552187</v>
       </c>
       <c r="R33" t="n">
-        <v>6992600</v>
+        <v>6992682</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4121,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617501</v>
+        <v>123617509</v>
       </c>
       <c r="B34" t="n">
-        <v>92299</v>
+        <v>79406</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4137,21 +4142,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4161,10 +4166,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552274</v>
+        <v>552284</v>
       </c>
       <c r="R34" t="n">
-        <v>6992684</v>
+        <v>6992593</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4197,11 +4202,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617524</v>
+        <v>123617514</v>
       </c>
       <c r="B35" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,25 +4240,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552103</v>
+        <v>552197</v>
       </c>
       <c r="R35" t="n">
-        <v>6992492</v>
+        <v>6992592</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617499</v>
+        <v>123617494</v>
       </c>
       <c r="B36" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4342,25 +4342,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552214</v>
+        <v>552187</v>
       </c>
       <c r="R36" t="n">
-        <v>6992683</v>
+        <v>6992682</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617512</v>
+        <v>123617503</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552221</v>
+        <v>552203</v>
       </c>
       <c r="R37" t="n">
-        <v>6992606</v>
+        <v>6992653</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617498</v>
+        <v>123617522</v>
       </c>
       <c r="B38" t="n">
-        <v>98079</v>
+        <v>79377</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552204</v>
+        <v>552067</v>
       </c>
       <c r="R38" t="n">
-        <v>6992680</v>
+        <v>6992564</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123617515</v>
+        <v>123617511</v>
       </c>
       <c r="B39" t="n">
-        <v>90955</v>
+        <v>80741</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4648,25 +4648,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>552174</v>
+        <v>552284</v>
       </c>
       <c r="R39" t="n">
-        <v>6992595</v>
+        <v>6992593</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123617493</v>
+        <v>123617521</v>
       </c>
       <c r="B40" t="n">
-        <v>98079</v>
+        <v>77716</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4750,25 +4750,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552189</v>
+        <v>552067</v>
       </c>
       <c r="R40" t="n">
-        <v>6992689</v>
+        <v>6992564</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2897,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123617493</v>
+        <v>123617515</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>90955</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,25 +2909,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552189</v>
+        <v>552174</v>
       </c>
       <c r="R22" t="n">
-        <v>6992689</v>
+        <v>6992595</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617515</v>
+        <v>123617493</v>
       </c>
       <c r="B23" t="n">
-        <v>90955</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3011,25 +3011,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552174</v>
+        <v>552189</v>
       </c>
       <c r="R23" t="n">
-        <v>6992595</v>
+        <v>6992689</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123617498</v>
+        <v>123617506</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552204</v>
+        <v>552200</v>
       </c>
       <c r="R26" t="n">
-        <v>6992680</v>
+        <v>6992631</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3616,7 +3616,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617506</v>
+        <v>123617498</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552200</v>
+        <v>552204</v>
       </c>
       <c r="R29" t="n">
-        <v>6992631</v>
+        <v>6992680</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617522</v>
+        <v>123617511</v>
       </c>
       <c r="B38" t="n">
-        <v>79377</v>
+        <v>80741</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4550,21 +4550,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552067</v>
+        <v>552284</v>
       </c>
       <c r="R38" t="n">
-        <v>6992564</v>
+        <v>6992593</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123617511</v>
+        <v>123617522</v>
       </c>
       <c r="B39" t="n">
-        <v>80741</v>
+        <v>79377</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,21 +4652,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>552284</v>
+        <v>552067</v>
       </c>
       <c r="R39" t="n">
-        <v>6992593</v>
+        <v>6992564</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123617504</v>
+        <v>123617497</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552209</v>
+        <v>552196</v>
       </c>
       <c r="R15" t="n">
-        <v>6992635</v>
+        <v>6992684</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617492</v>
+        <v>123617499</v>
       </c>
       <c r="B16" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,25 +2297,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552193</v>
+        <v>552214</v>
       </c>
       <c r="R16" t="n">
-        <v>6992693</v>
+        <v>6992683</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617500</v>
+        <v>123617501</v>
       </c>
       <c r="B17" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,25 +2399,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552262</v>
+        <v>552274</v>
       </c>
       <c r="R17" t="n">
         <v>6992684</v>
@@ -2463,6 +2463,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,10 +2494,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617520</v>
+        <v>123617491</v>
       </c>
       <c r="B18" t="n">
-        <v>78172</v>
+        <v>92271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,25 +2506,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,10 +2534,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552067</v>
+        <v>552187</v>
       </c>
       <c r="R18" t="n">
-        <v>6992564</v>
+        <v>6992769</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,10 +2596,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617512</v>
+        <v>123617495</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>80741</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,25 +2608,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2636,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552221</v>
+        <v>552187</v>
       </c>
       <c r="R19" t="n">
-        <v>6992606</v>
+        <v>6992682</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,7 +2698,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617497</v>
+        <v>123617493</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552196</v>
+        <v>552189</v>
       </c>
       <c r="R20" t="n">
-        <v>6992684</v>
+        <v>6992689</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617491</v>
+        <v>123617494</v>
       </c>
       <c r="B21" t="n">
-        <v>92271</v>
+        <v>79406</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,25 +2812,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,7 +2843,7 @@
         <v>552187</v>
       </c>
       <c r="R21" t="n">
-        <v>6992769</v>
+        <v>6992682</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123617515</v>
+        <v>123617522</v>
       </c>
       <c r="B22" t="n">
-        <v>90955</v>
+        <v>79377</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,25 +2914,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552174</v>
+        <v>552067</v>
       </c>
       <c r="R22" t="n">
-        <v>6992595</v>
+        <v>6992564</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,10 +3004,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617493</v>
+        <v>123617515</v>
       </c>
       <c r="B23" t="n">
-        <v>98079</v>
+        <v>90955</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3011,25 +3016,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3039,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552189</v>
+        <v>552174</v>
       </c>
       <c r="R23" t="n">
-        <v>6992689</v>
+        <v>6992595</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3101,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123617510</v>
+        <v>123617514</v>
       </c>
       <c r="B24" t="n">
-        <v>78525</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,25 +3118,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3141,10 +3146,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552284</v>
+        <v>552197</v>
       </c>
       <c r="R24" t="n">
-        <v>6992593</v>
+        <v>6992592</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3203,7 +3208,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123617496</v>
+        <v>123617513</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3243,10 +3248,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552187</v>
+        <v>552205</v>
       </c>
       <c r="R25" t="n">
-        <v>6992682</v>
+        <v>6992600</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3305,10 +3310,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123617506</v>
+        <v>123617523</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3317,25 +3322,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3350,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552200</v>
+        <v>552103</v>
       </c>
       <c r="R26" t="n">
-        <v>6992631</v>
+        <v>6992492</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3407,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123617523</v>
+        <v>123617506</v>
       </c>
       <c r="B27" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,25 +3424,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3447,10 +3452,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552103</v>
+        <v>552200</v>
       </c>
       <c r="R27" t="n">
-        <v>6992492</v>
+        <v>6992631</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3509,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123617501</v>
+        <v>123617492</v>
       </c>
       <c r="B28" t="n">
-        <v>92299</v>
+        <v>92271</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,25 +3526,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552274</v>
+        <v>552193</v>
       </c>
       <c r="R28" t="n">
-        <v>6992684</v>
+        <v>6992693</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3585,11 +3590,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3616,7 +3616,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617498</v>
+        <v>123617503</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552204</v>
+        <v>552203</v>
       </c>
       <c r="R29" t="n">
-        <v>6992680</v>
+        <v>6992653</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3718,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123617524</v>
+        <v>123617511</v>
       </c>
       <c r="B30" t="n">
-        <v>78433</v>
+        <v>80741</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552103</v>
+        <v>552284</v>
       </c>
       <c r="R30" t="n">
-        <v>6992492</v>
+        <v>6992593</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3820,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123617499</v>
+        <v>123617524</v>
       </c>
       <c r="B31" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,25 +3832,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>552214</v>
+        <v>552103</v>
       </c>
       <c r="R31" t="n">
-        <v>6992683</v>
+        <v>6992492</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123617513</v>
+        <v>123617512</v>
       </c>
       <c r="B32" t="n">
         <v>98079</v>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552205</v>
+        <v>552221</v>
       </c>
       <c r="R32" t="n">
-        <v>6992600</v>
+        <v>6992606</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617495</v>
+        <v>123617509</v>
       </c>
       <c r="B33" t="n">
-        <v>80741</v>
+        <v>79406</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4040,21 +4040,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552187</v>
+        <v>552284</v>
       </c>
       <c r="R33" t="n">
-        <v>6992682</v>
+        <v>6992593</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4126,10 +4126,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617509</v>
+        <v>123617510</v>
       </c>
       <c r="B34" t="n">
-        <v>79406</v>
+        <v>78525</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4142,21 +4142,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617514</v>
+        <v>123617521</v>
       </c>
       <c r="B35" t="n">
-        <v>98079</v>
+        <v>77716</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,25 +4240,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552197</v>
+        <v>552067</v>
       </c>
       <c r="R35" t="n">
-        <v>6992592</v>
+        <v>6992564</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617494</v>
+        <v>123617500</v>
       </c>
       <c r="B36" t="n">
-        <v>79406</v>
+        <v>92271</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4342,25 +4342,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552187</v>
+        <v>552262</v>
       </c>
       <c r="R36" t="n">
-        <v>6992682</v>
+        <v>6992684</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617503</v>
+        <v>123617498</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552203</v>
+        <v>552204</v>
       </c>
       <c r="R37" t="n">
-        <v>6992653</v>
+        <v>6992680</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617511</v>
+        <v>123617520</v>
       </c>
       <c r="B38" t="n">
-        <v>80741</v>
+        <v>78172</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4550,21 +4550,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552284</v>
+        <v>552067</v>
       </c>
       <c r="R38" t="n">
-        <v>6992593</v>
+        <v>6992564</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123617522</v>
+        <v>123617504</v>
       </c>
       <c r="B39" t="n">
-        <v>79377</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4648,25 +4648,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>552067</v>
+        <v>552209</v>
       </c>
       <c r="R39" t="n">
-        <v>6992564</v>
+        <v>6992635</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123617521</v>
+        <v>123617518</v>
       </c>
       <c r="B40" t="n">
-        <v>77716</v>
+        <v>79869</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552067</v>
+        <v>552178</v>
       </c>
       <c r="R40" t="n">
-        <v>6992564</v>
+        <v>6992557</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4814,6 +4814,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4840,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123617518</v>
+        <v>123617496</v>
       </c>
       <c r="B41" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4852,25 +4857,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4880,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552178</v>
+        <v>552187</v>
       </c>
       <c r="R41" t="n">
-        <v>6992557</v>
+        <v>6992682</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4916,11 +4921,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4945,6 +4945,1521 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128935574</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>552105</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6992474</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128935572</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80225</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>552170</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6992588</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128935580</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92825</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>552203</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6992734</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128935566</v>
+      </c>
+      <c r="B45" t="n">
+        <v>88805</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>816</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Smultronkantarell</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Aphroditeola olida</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>552203</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6992734</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128935570</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91426</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>552290</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6992648</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128935577</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92806</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>552079</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6992455</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128935578</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>552061</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6992480</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128935579</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>552082</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6992490</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128935568</v>
+      </c>
+      <c r="B50" t="n">
+        <v>96878</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>53</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>552214</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6992674</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128935569</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>552229</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6992651</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128935573</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90536</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>552099</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6992505</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128935571</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>552188</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6992593</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128935575</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>552093</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6992465</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128935576</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>552087</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6992461</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128935567</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sandmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>552202</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6992679</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128935572</v>
       </c>
       <c r="B43" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>92825</v>
+        <v>92829</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88805</v>
+        <v>88809</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91426</v>
+        <v>91430</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5553,32 +5553,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935578</v>
+        <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>57876</v>
+        <v>92798</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552061</v>
+        <v>552082</v>
       </c>
       <c r="R48" t="n">
-        <v>6992480</v>
+        <v>6992490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935579</v>
+        <v>128935578</v>
       </c>
       <c r="B49" t="n">
-        <v>92794</v>
+        <v>57880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552082</v>
+        <v>552061</v>
       </c>
       <c r="R49" t="n">
-        <v>6992490</v>
+        <v>6992480</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5758,7 +5758,7 @@
         <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6260,37 +6260,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128935576</v>
+        <v>128935567</v>
       </c>
       <c r="B55" t="n">
-        <v>92794</v>
+        <v>98636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>552087</v>
+        <v>552202</v>
       </c>
       <c r="R55" t="n">
-        <v>6992461</v>
+        <v>6992679</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6361,37 +6361,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128935567</v>
+        <v>128935576</v>
       </c>
       <c r="B56" t="n">
-        <v>98632</v>
+        <v>92798</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>552202</v>
+        <v>552087</v>
       </c>
       <c r="R56" t="n">
-        <v>6992679</v>
+        <v>6992461</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -5452,10 +5452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935577</v>
+        <v>128935579</v>
       </c>
       <c r="B47" t="n">
-        <v>92810</v>
+        <v>92798</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5463,21 +5463,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552079</v>
+        <v>552082</v>
       </c>
       <c r="R47" t="n">
-        <v>6992455</v>
+        <v>6992490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935579</v>
+        <v>128935577</v>
       </c>
       <c r="B48" t="n">
-        <v>92798</v>
+        <v>92810</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552082</v>
+        <v>552079</v>
       </c>
       <c r="R48" t="n">
-        <v>6992490</v>
+        <v>6992455</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6260,37 +6260,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128935567</v>
+        <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>98636</v>
+        <v>92798</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>552202</v>
+        <v>552087</v>
       </c>
       <c r="R55" t="n">
-        <v>6992679</v>
+        <v>6992461</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6361,37 +6361,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128935576</v>
+        <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>92798</v>
+        <v>98636</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>552087</v>
+        <v>552202</v>
       </c>
       <c r="R56" t="n">
-        <v>6992461</v>
+        <v>6992679</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5048,32 +5048,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128935572</v>
+        <v>128935580</v>
       </c>
       <c r="B43" t="n">
-        <v>80229</v>
+        <v>92834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>552170</v>
+        <v>552203</v>
       </c>
       <c r="R43" t="n">
-        <v>6992588</v>
+        <v>6992734</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5149,32 +5149,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128935580</v>
+        <v>128935572</v>
       </c>
       <c r="B44" t="n">
-        <v>92829</v>
+        <v>80134</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>232140</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552203</v>
+        <v>552170</v>
       </c>
       <c r="R44" t="n">
-        <v>6992734</v>
+        <v>6992588</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88809</v>
+        <v>88814</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91430</v>
+        <v>91435</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,10 +5452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935579</v>
+        <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>92798</v>
+        <v>92815</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5463,21 +5463,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552082</v>
+        <v>552079</v>
       </c>
       <c r="R47" t="n">
-        <v>6992490</v>
+        <v>6992455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935577</v>
+        <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>92810</v>
+        <v>92803</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552079</v>
+        <v>552082</v>
       </c>
       <c r="R48" t="n">
-        <v>6992455</v>
+        <v>6992490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5657,7 +5657,7 @@
         <v>128935578</v>
       </c>
       <c r="B49" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5755,37 +5755,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128935568</v>
+        <v>128935569</v>
       </c>
       <c r="B50" t="n">
-        <v>96882</v>
+        <v>98643</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552214</v>
+        <v>552229</v>
       </c>
       <c r="R50" t="n">
-        <v>6992674</v>
+        <v>6992651</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128935569</v>
+        <v>128935568</v>
       </c>
       <c r="B51" t="n">
-        <v>98636</v>
+        <v>96889</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>552229</v>
+        <v>552214</v>
       </c>
       <c r="R51" t="n">
-        <v>6992651</v>
+        <v>6992674</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -5048,32 +5048,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128935580</v>
+        <v>128935572</v>
       </c>
       <c r="B43" t="n">
-        <v>92842</v>
+        <v>80139</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>232140</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>552203</v>
+        <v>552170</v>
       </c>
       <c r="R43" t="n">
-        <v>6992734</v>
+        <v>6992588</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5149,32 +5149,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128935572</v>
+        <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>80139</v>
+        <v>92842</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552170</v>
+        <v>552203</v>
       </c>
       <c r="R44" t="n">
-        <v>6992588</v>
+        <v>6992734</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5755,37 +5755,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128935568</v>
+        <v>128935569</v>
       </c>
       <c r="B50" t="n">
-        <v>96897</v>
+        <v>98651</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552214</v>
+        <v>552229</v>
       </c>
       <c r="R50" t="n">
-        <v>6992674</v>
+        <v>6992651</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128935569</v>
+        <v>128935568</v>
       </c>
       <c r="B51" t="n">
-        <v>98651</v>
+        <v>96897</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>552229</v>
+        <v>552214</v>
       </c>
       <c r="R51" t="n">
-        <v>6992651</v>
+        <v>6992674</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88821</v>
+        <v>88824</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91442</v>
+        <v>91445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,10 +5452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935579</v>
+        <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>92811</v>
+        <v>92828</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5463,21 +5463,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552082</v>
+        <v>552079</v>
       </c>
       <c r="R47" t="n">
-        <v>6992490</v>
+        <v>6992455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935577</v>
+        <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>92823</v>
+        <v>92816</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552079</v>
+        <v>552082</v>
       </c>
       <c r="R48" t="n">
-        <v>6992455</v>
+        <v>6992490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5758,7 +5758,7 @@
         <v>128935569</v>
       </c>
       <c r="B50" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>128935568</v>
       </c>
       <c r="B51" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128935572</v>
       </c>
       <c r="B43" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>92847</v>
+        <v>92850</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88824</v>
+        <v>88827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91445</v>
+        <v>91448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>128935569</v>
       </c>
       <c r="B50" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>128935568</v>
       </c>
       <c r="B51" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6260,37 +6260,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128935576</v>
+        <v>128935567</v>
       </c>
       <c r="B55" t="n">
-        <v>92816</v>
+        <v>98659</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>552087</v>
+        <v>552202</v>
       </c>
       <c r="R55" t="n">
-        <v>6992461</v>
+        <v>6992679</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6361,37 +6361,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128935567</v>
+        <v>128935576</v>
       </c>
       <c r="B56" t="n">
-        <v>98656</v>
+        <v>92819</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>552202</v>
+        <v>552087</v>
       </c>
       <c r="R56" t="n">
-        <v>6992679</v>
+        <v>6992461</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -5755,37 +5755,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128935569</v>
+        <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>96905</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552229</v>
+        <v>552214</v>
       </c>
       <c r="R50" t="n">
-        <v>6992651</v>
+        <v>6992674</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128935568</v>
+        <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>96905</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>552214</v>
+        <v>552229</v>
       </c>
       <c r="R51" t="n">
-        <v>6992674</v>
+        <v>6992651</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -5553,32 +5553,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935579</v>
+        <v>128935578</v>
       </c>
       <c r="B48" t="n">
-        <v>92819</v>
+        <v>57883</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552082</v>
+        <v>552061</v>
       </c>
       <c r="R48" t="n">
-        <v>6992490</v>
+        <v>6992480</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935578</v>
+        <v>128935579</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>92819</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552061</v>
+        <v>552082</v>
       </c>
       <c r="R49" t="n">
-        <v>6992480</v>
+        <v>6992490</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5755,37 +5755,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128935568</v>
+        <v>128935569</v>
       </c>
       <c r="B50" t="n">
-        <v>96905</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552214</v>
+        <v>552229</v>
       </c>
       <c r="R50" t="n">
-        <v>6992674</v>
+        <v>6992651</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128935569</v>
+        <v>128935568</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>96905</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>552229</v>
+        <v>552214</v>
       </c>
       <c r="R51" t="n">
-        <v>6992651</v>
+        <v>6992674</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -5048,32 +5048,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128935572</v>
+        <v>128935580</v>
       </c>
       <c r="B43" t="n">
-        <v>80140</v>
+        <v>92850</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>552170</v>
+        <v>552203</v>
       </c>
       <c r="R43" t="n">
-        <v>6992588</v>
+        <v>6992734</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5149,32 +5149,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128935580</v>
+        <v>128935572</v>
       </c>
       <c r="B44" t="n">
-        <v>92850</v>
+        <v>80140</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>232140</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552203</v>
+        <v>552170</v>
       </c>
       <c r="R44" t="n">
-        <v>6992734</v>
+        <v>6992588</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5553,32 +5553,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935578</v>
+        <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>57883</v>
+        <v>92819</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552061</v>
+        <v>552082</v>
       </c>
       <c r="R48" t="n">
-        <v>6992480</v>
+        <v>6992490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935579</v>
+        <v>128935578</v>
       </c>
       <c r="B49" t="n">
-        <v>92819</v>
+        <v>57883</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552082</v>
+        <v>552061</v>
       </c>
       <c r="R49" t="n">
-        <v>6992490</v>
+        <v>6992480</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6260,37 +6260,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128935567</v>
+        <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>552202</v>
+        <v>552087</v>
       </c>
       <c r="R55" t="n">
-        <v>6992679</v>
+        <v>6992461</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6361,37 +6361,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128935576</v>
+        <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>552087</v>
+        <v>552202</v>
       </c>
       <c r="R56" t="n">
-        <v>6992461</v>
+        <v>6992679</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128935580</v>
       </c>
       <c r="B43" t="n">
-        <v>92850</v>
+        <v>92857</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>128935572</v>
       </c>
       <c r="B44" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88827</v>
+        <v>88831</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,10 +5452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935577</v>
+        <v>128935579</v>
       </c>
       <c r="B47" t="n">
-        <v>92831</v>
+        <v>92826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5463,21 +5463,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552079</v>
+        <v>552082</v>
       </c>
       <c r="R47" t="n">
-        <v>6992455</v>
+        <v>6992490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,32 +5553,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935579</v>
+        <v>128935578</v>
       </c>
       <c r="B48" t="n">
-        <v>92819</v>
+        <v>57885</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552082</v>
+        <v>552061</v>
       </c>
       <c r="R48" t="n">
-        <v>6992490</v>
+        <v>6992480</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935578</v>
+        <v>128935577</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>92838</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552061</v>
+        <v>552079</v>
       </c>
       <c r="R49" t="n">
-        <v>6992480</v>
+        <v>6992455</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5758,7 +5758,7 @@
         <v>128935569</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>128935568</v>
       </c>
       <c r="B51" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -5048,32 +5048,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128935580</v>
+        <v>128935572</v>
       </c>
       <c r="B43" t="n">
-        <v>92857</v>
+        <v>80144</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>232140</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>552203</v>
+        <v>552170</v>
       </c>
       <c r="R43" t="n">
-        <v>6992734</v>
+        <v>6992588</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5149,32 +5149,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128935572</v>
+        <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>80144</v>
+        <v>92857</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552170</v>
+        <v>552203</v>
       </c>
       <c r="R44" t="n">
-        <v>6992588</v>
+        <v>6992734</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5452,10 +5452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935579</v>
+        <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>92826</v>
+        <v>92838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5463,21 +5463,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552082</v>
+        <v>552079</v>
       </c>
       <c r="R47" t="n">
-        <v>6992490</v>
+        <v>6992455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,32 +5553,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935578</v>
+        <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>57885</v>
+        <v>92826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552061</v>
+        <v>552082</v>
       </c>
       <c r="R48" t="n">
-        <v>6992480</v>
+        <v>6992490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935577</v>
+        <v>128935578</v>
       </c>
       <c r="B49" t="n">
-        <v>92838</v>
+        <v>57885</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552079</v>
+        <v>552061</v>
       </c>
       <c r="R49" t="n">
-        <v>6992455</v>
+        <v>6992480</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5755,37 +5755,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128935569</v>
+        <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>98669</v>
+        <v>96915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552229</v>
+        <v>552214</v>
       </c>
       <c r="R50" t="n">
-        <v>6992651</v>
+        <v>6992674</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128935568</v>
+        <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>96915</v>
+        <v>98669</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>552214</v>
+        <v>552229</v>
       </c>
       <c r="R51" t="n">
-        <v>6992674</v>
+        <v>6992651</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88831</v>
+        <v>88838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91454</v>
+        <v>91461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935577</v>
+        <v>128935578</v>
       </c>
       <c r="B47" t="n">
-        <v>92838</v>
+        <v>57885</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552079</v>
+        <v>552061</v>
       </c>
       <c r="R47" t="n">
-        <v>6992455</v>
+        <v>6992480</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935579</v>
+        <v>128935577</v>
       </c>
       <c r="B48" t="n">
-        <v>92826</v>
+        <v>92845</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552082</v>
+        <v>552079</v>
       </c>
       <c r="R48" t="n">
-        <v>6992490</v>
+        <v>6992455</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935578</v>
+        <v>128935579</v>
       </c>
       <c r="B49" t="n">
-        <v>57885</v>
+        <v>92833</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552061</v>
+        <v>552082</v>
       </c>
       <c r="R49" t="n">
-        <v>6992480</v>
+        <v>6992490</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5758,7 +5758,7 @@
         <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128935572</v>
       </c>
       <c r="B43" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>92864</v>
+        <v>92866</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88838</v>
+        <v>88840</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91461</v>
+        <v>91463</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935578</v>
+        <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>57885</v>
+        <v>92847</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552061</v>
+        <v>552079</v>
       </c>
       <c r="R47" t="n">
-        <v>6992480</v>
+        <v>6992455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935577</v>
+        <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>92845</v>
+        <v>92835</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552079</v>
+        <v>552082</v>
       </c>
       <c r="R48" t="n">
-        <v>6992455</v>
+        <v>6992490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935579</v>
+        <v>128935578</v>
       </c>
       <c r="B49" t="n">
-        <v>92833</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552082</v>
+        <v>552061</v>
       </c>
       <c r="R49" t="n">
-        <v>6992490</v>
+        <v>6992480</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5758,7 +5758,7 @@
         <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935577</v>
+        <v>128935578</v>
       </c>
       <c r="B47" t="n">
-        <v>92847</v>
+        <v>57887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552079</v>
+        <v>552061</v>
       </c>
       <c r="R47" t="n">
-        <v>6992455</v>
+        <v>6992480</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935579</v>
+        <v>128935577</v>
       </c>
       <c r="B48" t="n">
-        <v>92835</v>
+        <v>92847</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552082</v>
+        <v>552079</v>
       </c>
       <c r="R48" t="n">
-        <v>6992490</v>
+        <v>6992455</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935578</v>
+        <v>128935579</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>92835</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552061</v>
+        <v>552082</v>
       </c>
       <c r="R49" t="n">
-        <v>6992480</v>
+        <v>6992490</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935578</v>
+        <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>57887</v>
+        <v>92847</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552061</v>
+        <v>552079</v>
       </c>
       <c r="R47" t="n">
-        <v>6992480</v>
+        <v>6992455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935577</v>
+        <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>92847</v>
+        <v>92835</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552079</v>
+        <v>552082</v>
       </c>
       <c r="R48" t="n">
-        <v>6992455</v>
+        <v>6992490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935579</v>
+        <v>128935578</v>
       </c>
       <c r="B49" t="n">
-        <v>92835</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552082</v>
+        <v>552061</v>
       </c>
       <c r="R49" t="n">
-        <v>6992490</v>
+        <v>6992480</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5755,37 +5755,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128935568</v>
+        <v>128935569</v>
       </c>
       <c r="B50" t="n">
-        <v>96924</v>
+        <v>98678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552214</v>
+        <v>552229</v>
       </c>
       <c r="R50" t="n">
-        <v>6992674</v>
+        <v>6992651</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128935569</v>
+        <v>128935568</v>
       </c>
       <c r="B51" t="n">
-        <v>98678</v>
+        <v>96924</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>552229</v>
+        <v>552214</v>
       </c>
       <c r="R51" t="n">
-        <v>6992651</v>
+        <v>6992674</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>92866</v>
+        <v>92852</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88840</v>
+        <v>88841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935577</v>
+        <v>128935578</v>
       </c>
       <c r="B47" t="n">
-        <v>92847</v>
+        <v>57887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552079</v>
+        <v>552061</v>
       </c>
       <c r="R47" t="n">
-        <v>6992455</v>
+        <v>6992480</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935579</v>
+        <v>128935577</v>
       </c>
       <c r="B48" t="n">
-        <v>92835</v>
+        <v>92833</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552082</v>
+        <v>552079</v>
       </c>
       <c r="R48" t="n">
-        <v>6992490</v>
+        <v>6992455</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935578</v>
+        <v>128935579</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>92821</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552061</v>
+        <v>552082</v>
       </c>
       <c r="R49" t="n">
-        <v>6992480</v>
+        <v>6992490</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5755,37 +5755,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128935569</v>
+        <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>98678</v>
+        <v>96950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552229</v>
+        <v>552214</v>
       </c>
       <c r="R50" t="n">
-        <v>6992651</v>
+        <v>6992674</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128935568</v>
+        <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>96924</v>
+        <v>98704</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>552214</v>
+        <v>552229</v>
       </c>
       <c r="R51" t="n">
-        <v>6992674</v>
+        <v>6992651</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>92852</v>
+        <v>92853</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935578</v>
+        <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>57887</v>
+        <v>92834</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552061</v>
+        <v>552079</v>
       </c>
       <c r="R47" t="n">
-        <v>6992480</v>
+        <v>6992455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935577</v>
+        <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>92833</v>
+        <v>92822</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552079</v>
+        <v>552082</v>
       </c>
       <c r="R48" t="n">
-        <v>6992455</v>
+        <v>6992490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935579</v>
+        <v>128935578</v>
       </c>
       <c r="B49" t="n">
-        <v>92821</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552082</v>
+        <v>552061</v>
       </c>
       <c r="R49" t="n">
-        <v>6992490</v>
+        <v>6992480</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5758,7 +5758,7 @@
         <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935577</v>
+        <v>128935578</v>
       </c>
       <c r="B47" t="n">
-        <v>92834</v>
+        <v>57887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552079</v>
+        <v>552061</v>
       </c>
       <c r="R47" t="n">
-        <v>6992455</v>
+        <v>6992480</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935579</v>
+        <v>128935577</v>
       </c>
       <c r="B48" t="n">
-        <v>92822</v>
+        <v>92834</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552082</v>
+        <v>552079</v>
       </c>
       <c r="R48" t="n">
-        <v>6992490</v>
+        <v>6992455</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935578</v>
+        <v>128935579</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>92822</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552061</v>
+        <v>552082</v>
       </c>
       <c r="R49" t="n">
-        <v>6992480</v>
+        <v>6992490</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5755,37 +5755,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128935568</v>
+        <v>128935569</v>
       </c>
       <c r="B50" t="n">
-        <v>96951</v>
+        <v>98706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552214</v>
+        <v>552229</v>
       </c>
       <c r="R50" t="n">
-        <v>6992674</v>
+        <v>6992651</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128935569</v>
+        <v>128935568</v>
       </c>
       <c r="B51" t="n">
-        <v>98705</v>
+        <v>96952</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>552229</v>
+        <v>552214</v>
       </c>
       <c r="R51" t="n">
-        <v>6992651</v>
+        <v>6992674</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5048,32 +5048,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128935572</v>
+        <v>128935580</v>
       </c>
       <c r="B43" t="n">
-        <v>80146</v>
+        <v>92856</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>552170</v>
+        <v>552203</v>
       </c>
       <c r="R43" t="n">
-        <v>6992588</v>
+        <v>6992734</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5149,32 +5149,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128935580</v>
+        <v>128935572</v>
       </c>
       <c r="B44" t="n">
-        <v>92853</v>
+        <v>80148</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>232140</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552203</v>
+        <v>552170</v>
       </c>
       <c r="R44" t="n">
-        <v>6992734</v>
+        <v>6992588</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88841</v>
+        <v>88844</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91463</v>
+        <v>91466</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935578</v>
+        <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>57887</v>
+        <v>92837</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552061</v>
+        <v>552079</v>
       </c>
       <c r="R47" t="n">
-        <v>6992480</v>
+        <v>6992455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935577</v>
+        <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>92834</v>
+        <v>92825</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552079</v>
+        <v>552082</v>
       </c>
       <c r="R48" t="n">
-        <v>6992455</v>
+        <v>6992490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935579</v>
+        <v>128935578</v>
       </c>
       <c r="B49" t="n">
-        <v>92822</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552082</v>
+        <v>552061</v>
       </c>
       <c r="R49" t="n">
-        <v>6992490</v>
+        <v>6992480</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5755,37 +5755,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128935569</v>
+        <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>98706</v>
+        <v>96956</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552229</v>
+        <v>552214</v>
       </c>
       <c r="R50" t="n">
-        <v>6992651</v>
+        <v>6992674</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5856,37 +5856,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128935568</v>
+        <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>96952</v>
+        <v>98710</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>552214</v>
+        <v>552229</v>
       </c>
       <c r="R51" t="n">
-        <v>6992674</v>
+        <v>6992651</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128935580</v>
       </c>
       <c r="B43" t="n">
-        <v>92856</v>
+        <v>92858</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>128935572</v>
       </c>
       <c r="B44" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88844</v>
+        <v>88846</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91466</v>
+        <v>91468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5553,32 +5553,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935579</v>
+        <v>128935578</v>
       </c>
       <c r="B48" t="n">
-        <v>92825</v>
+        <v>57887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552082</v>
+        <v>552061</v>
       </c>
       <c r="R48" t="n">
-        <v>6992490</v>
+        <v>6992480</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935578</v>
+        <v>128935579</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>92827</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552061</v>
+        <v>552082</v>
       </c>
       <c r="R49" t="n">
-        <v>6992480</v>
+        <v>6992490</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5758,7 +5758,7 @@
         <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5048,32 +5048,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128935580</v>
+        <v>128935572</v>
       </c>
       <c r="B43" t="n">
-        <v>92858</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>232140</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>552203</v>
+        <v>552170</v>
       </c>
       <c r="R43" t="n">
-        <v>6992734</v>
+        <v>6992588</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5149,32 +5149,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128935572</v>
+        <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>92862</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>552170</v>
+        <v>552203</v>
       </c>
       <c r="R44" t="n">
-        <v>6992588</v>
+        <v>6992734</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88846</v>
+        <v>88850</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91468</v>
+        <v>91472</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935577</v>
+        <v>128935578</v>
       </c>
       <c r="B47" t="n">
-        <v>92839</v>
+        <v>57887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552079</v>
+        <v>552061</v>
       </c>
       <c r="R47" t="n">
-        <v>6992455</v>
+        <v>6992480</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,32 +5553,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935578</v>
+        <v>128935577</v>
       </c>
       <c r="B48" t="n">
-        <v>57887</v>
+        <v>92843</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552061</v>
+        <v>552079</v>
       </c>
       <c r="R48" t="n">
-        <v>6992480</v>
+        <v>6992455</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5657,7 +5657,7 @@
         <v>128935579</v>
       </c>
       <c r="B49" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>128935576</v>
       </c>
       <c r="B55" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>128935567</v>
       </c>
       <c r="B56" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -4950,7 +4950,7 @@
         <v>128935574</v>
       </c>
       <c r="B42" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>128935580</v>
       </c>
       <c r="B44" t="n">
-        <v>92862</v>
+        <v>92863</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>128935566</v>
       </c>
       <c r="B45" t="n">
-        <v>88850</v>
+        <v>88851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128935570</v>
       </c>
       <c r="B46" t="n">
-        <v>91472</v>
+        <v>91473</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5452,32 +5452,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935578</v>
+        <v>128935577</v>
       </c>
       <c r="B47" t="n">
-        <v>57887</v>
+        <v>92844</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552061</v>
+        <v>552079</v>
       </c>
       <c r="R47" t="n">
-        <v>6992480</v>
+        <v>6992455</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935577</v>
+        <v>128935579</v>
       </c>
       <c r="B48" t="n">
-        <v>92843</v>
+        <v>92832</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552079</v>
+        <v>552082</v>
       </c>
       <c r="R48" t="n">
-        <v>6992455</v>
+        <v>6992490</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5654,32 +5654,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935579</v>
+        <v>128935578</v>
       </c>
       <c r="B49" t="n">
-        <v>92831</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552082</v>
+        <v>552061</v>
       </c>
       <c r="R49" t="n">
-        <v>6992490</v>
+        <v>6992480</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5758,7 +5758,7 @@
         <v>128935568</v>
       </c>
       <c r="B50" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>128935573</v>
       </c>
       <c r="B52" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>128935571</v>
       </c>
       <c r="B53" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>128935575</v>
       </c>
       <c r="B54" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6260,37 +6260,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128935576</v>
+        <v>128935567</v>
       </c>
       <c r="B55" t="n">
-        <v>92831</v>
+        <v>98724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>552087</v>
+        <v>552202</v>
       </c>
       <c r="R55" t="n">
-        <v>6992461</v>
+        <v>6992679</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6361,37 +6361,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128935567</v>
+        <v>128935576</v>
       </c>
       <c r="B56" t="n">
-        <v>98716</v>
+        <v>92832</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>552202</v>
+        <v>552087</v>
       </c>
       <c r="R56" t="n">
-        <v>6992679</v>
+        <v>6992461</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97365564</v>
+        <v>128935568</v>
       </c>
       <c r="B2" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552229.7305869955</v>
+        <v>552214</v>
       </c>
       <c r="R2" t="n">
-        <v>6992727.166794822</v>
+        <v>6992674</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,53 +764,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97365563</v>
+        <v>97365525</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552211.6346826437</v>
+        <v>552085</v>
       </c>
       <c r="R3" t="n">
-        <v>6992722.794128449</v>
+        <v>6992546</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2021-10-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97365539</v>
+        <v>97365556</v>
       </c>
       <c r="B4" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552221.0079583335</v>
+        <v>552062</v>
       </c>
       <c r="R4" t="n">
-        <v>6992619.992336879</v>
+        <v>6992478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2021-10-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97365544</v>
+        <v>123617524</v>
       </c>
       <c r="B5" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6457</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1013,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552214.9063167963</v>
+        <v>552103</v>
       </c>
       <c r="R5" t="n">
-        <v>6992604.020236146</v>
+        <v>6992492</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,64 +1068,59 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97365551</v>
+        <v>128935566</v>
       </c>
       <c r="B6" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>816</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552193.9318666979</v>
+        <v>552203</v>
       </c>
       <c r="R6" t="n">
-        <v>6992778.746597758</v>
+        <v>6992734</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,31 +1164,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97365537</v>
+        <v>123617495</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,13 +1211,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552174.3618376546</v>
+        <v>552187</v>
       </c>
       <c r="R7" t="n">
-        <v>6992583.412769449</v>
+        <v>6992682</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1241,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,26 +1266,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97365525</v>
+        <v>123617511</v>
       </c>
       <c r="B8" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,13 +1308,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552085.0327907131</v>
+        <v>552284</v>
       </c>
       <c r="R8" t="n">
-        <v>6992546.148859281</v>
+        <v>6992593</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,22 +1338,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,26 +1363,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97365556</v>
+        <v>128935571</v>
       </c>
       <c r="B9" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,37 +1381,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552061.5961644105</v>
+        <v>552188</v>
       </c>
       <c r="R9" t="n">
-        <v>6992478.193254936</v>
+        <v>6992593</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,22 +1439,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,69 +1459,64 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97365555</v>
+        <v>128935573</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552114.5862832363</v>
+        <v>552099</v>
       </c>
       <c r="R10" t="n">
-        <v>6992572.475199082</v>
+        <v>6992505</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,22 +1540,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,69 +1560,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97365530</v>
+        <v>128935570</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552079.4101166956</v>
+        <v>552290</v>
       </c>
       <c r="R11" t="n">
-        <v>6992500.249655514</v>
+        <v>6992648</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1789,22 +1641,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,31 +1661,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97365534</v>
+        <v>97365530</v>
       </c>
       <c r="B12" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552098.0374221022</v>
+        <v>552079</v>
       </c>
       <c r="R12" t="n">
-        <v>6992528.215269874</v>
+        <v>6992500</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,19 +1741,9 @@
           <t>2021-10-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,15 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97365538</v>
+        <v>97365550</v>
       </c>
       <c r="B13" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552207.1621103551</v>
+        <v>551998</v>
       </c>
       <c r="R13" t="n">
-        <v>6992746.75913102</v>
+        <v>6992410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,19 +1842,9 @@
           <t>2021-10-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,37 +1875,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97365532</v>
+        <v>97365555</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2107,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552172.4655013118</v>
+        <v>552115</v>
       </c>
       <c r="R14" t="n">
-        <v>6992588.371326801</v>
+        <v>6992573</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,19 +1943,9 @@
           <t>2021-10-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,15 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123617495</v>
+        <v>97365563</v>
       </c>
       <c r="B15" t="n">
-        <v>80763</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,13 +2011,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552187</v>
+        <v>552212</v>
       </c>
       <c r="R15" t="n">
-        <v>6992682</v>
+        <v>6992723</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2253,12 +2041,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,44 +2066,43 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123617496</v>
+        <v>123617491</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,7 +2115,7 @@
         <v>552187</v>
       </c>
       <c r="R16" t="n">
-        <v>6992682</v>
+        <v>6992769</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2387,37 +2174,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617493</v>
+        <v>123617492</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2427,10 +2209,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552189</v>
+        <v>552193</v>
       </c>
       <c r="R17" t="n">
-        <v>6992689</v>
+        <v>6992693</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2489,37 +2271,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617498</v>
+        <v>123617500</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2529,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552204</v>
+        <v>552262</v>
       </c>
       <c r="R18" t="n">
-        <v>6992680</v>
+        <v>6992684</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2591,37 +2368,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617497</v>
+        <v>123617523</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552196</v>
+        <v>552103</v>
       </c>
       <c r="R19" t="n">
-        <v>6992684</v>
+        <v>6992492</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,15 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617501</v>
+        <v>128935574</v>
       </c>
       <c r="B20" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,37 +2476,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552274</v>
+        <v>552105</v>
       </c>
       <c r="R20" t="n">
-        <v>6992684</v>
+        <v>6992474</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2763,24 +2534,19 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp.</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2788,27 +2554,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617509</v>
+        <v>128935576</v>
       </c>
       <c r="B21" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,37 +2577,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552284</v>
+        <v>552087</v>
       </c>
       <c r="R21" t="n">
-        <v>6992593</v>
+        <v>6992461</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2870,12 +2635,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,31 +2655,26 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123617500</v>
+        <v>128935579</v>
       </c>
       <c r="B22" t="n">
-        <v>92293</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2935,20 +2695,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552262</v>
+        <v>552082</v>
       </c>
       <c r="R22" t="n">
-        <v>6992684</v>
+        <v>6992490</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2972,12 +2736,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,65 +2756,64 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123617512</v>
+        <v>128935577</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552221</v>
+        <v>552079</v>
       </c>
       <c r="R23" t="n">
-        <v>6992606</v>
+        <v>6992455</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3074,12 +2837,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3094,49 +2857,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123617521</v>
+        <v>123617515</v>
       </c>
       <c r="B24" t="n">
-        <v>77738</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3146,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552067</v>
+        <v>552174</v>
       </c>
       <c r="R24" t="n">
-        <v>6992564</v>
+        <v>6992595</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3208,53 +2966,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123617492</v>
+        <v>128935575</v>
       </c>
       <c r="B25" t="n">
-        <v>92293</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552193</v>
+        <v>552093</v>
       </c>
       <c r="R25" t="n">
-        <v>6992693</v>
+        <v>6992465</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3278,12 +3035,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,49 +3055,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123617491</v>
+        <v>123617520</v>
       </c>
       <c r="B26" t="n">
-        <v>92293</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3350,10 +3102,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552187</v>
+        <v>552067</v>
       </c>
       <c r="R26" t="n">
-        <v>6992769</v>
+        <v>6992564</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3412,37 +3164,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123617518</v>
+        <v>97365539</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3452,13 +3199,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552178</v>
+        <v>552221</v>
       </c>
       <c r="R27" t="n">
-        <v>6992557</v>
+        <v>6992620</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3482,17 +3229,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,22 +3254,21 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123617522</v>
+        <v>97365538</v>
       </c>
       <c r="B28" t="n">
-        <v>79399</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,21 +3276,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3559,13 +3300,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552067</v>
+        <v>552208</v>
       </c>
       <c r="R28" t="n">
-        <v>6992564</v>
+        <v>6992746</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3589,12 +3330,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3614,44 +3355,43 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123617514</v>
+        <v>123617494</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3661,10 +3401,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>552197</v>
+        <v>552187</v>
       </c>
       <c r="R29" t="n">
-        <v>6992592</v>
+        <v>6992682</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3723,37 +3463,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123617503</v>
+        <v>123617509</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3498,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552203</v>
+        <v>552284</v>
       </c>
       <c r="R30" t="n">
-        <v>6992653</v>
+        <v>6992593</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3825,15 +3560,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123617515</v>
+        <v>97365544</v>
       </c>
       <c r="B31" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3841,21 +3571,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6457</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3865,13 +3595,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>552174</v>
+        <v>552215</v>
       </c>
       <c r="R31" t="n">
-        <v>6992595</v>
+        <v>6992604</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3895,12 +3625,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3920,44 +3650,43 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123617499</v>
+        <v>97365537</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,13 +3696,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552214</v>
+        <v>552174</v>
       </c>
       <c r="R32" t="n">
-        <v>6992683</v>
+        <v>6992584</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3997,12 +3726,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4022,22 +3751,21 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123617520</v>
+        <v>123617518</v>
       </c>
       <c r="B33" t="n">
-        <v>78194</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4045,21 +3773,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4069,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>552067</v>
+        <v>552178</v>
       </c>
       <c r="R33" t="n">
-        <v>6992564</v>
+        <v>6992557</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4105,6 +3833,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4131,15 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123617511</v>
+        <v>128935572</v>
       </c>
       <c r="B34" t="n">
-        <v>80763</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4147,37 +3875,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>552284</v>
+        <v>552170</v>
       </c>
       <c r="R34" t="n">
-        <v>6992593</v>
+        <v>6992588</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4201,12 +3933,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4221,49 +3953,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123617506</v>
+        <v>97365564</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4273,13 +4000,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552200</v>
+        <v>552229</v>
       </c>
       <c r="R35" t="n">
-        <v>6992631</v>
+        <v>6992727</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4303,12 +4030,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4328,44 +4055,43 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123617504</v>
+        <v>123617521</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4375,10 +4101,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552209</v>
+        <v>552067</v>
       </c>
       <c r="R36" t="n">
-        <v>6992635</v>
+        <v>6992564</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4437,15 +4163,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123617524</v>
+        <v>128935578</v>
       </c>
       <c r="B37" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,37 +4174,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sandmon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552103</v>
+        <v>552061</v>
       </c>
       <c r="R37" t="n">
-        <v>6992492</v>
+        <v>6992480</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4507,12 +4232,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,49 +4252,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123617523</v>
+        <v>97365532</v>
       </c>
       <c r="B38" t="n">
-        <v>92293</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4579,13 +4299,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552103</v>
+        <v>552172</v>
       </c>
       <c r="R38" t="n">
-        <v>6992492</v>
+        <v>6992589</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4609,12 +4329,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,44 +4354,43 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123617494</v>
+        <v>123617493</v>
       </c>
       <c r="B39" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4681,10 +4400,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>552187</v>
+        <v>552189</v>
       </c>
       <c r="R39" t="n">
-        <v>6992682</v>
+        <v>6992689</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4743,37 +4462,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123617510</v>
+        <v>123617496</v>
       </c>
       <c r="B40" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4783,10 +4497,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>552284</v>
+        <v>552187</v>
       </c>
       <c r="R40" t="n">
-        <v>6992593</v>
+        <v>6992682</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4845,15 +4559,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123617513</v>
+        <v>123617497</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4885,10 +4594,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552205</v>
+        <v>552196</v>
       </c>
       <c r="R41" t="n">
-        <v>6992600</v>
+        <v>6992684</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4947,52 +4656,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128935574</v>
+        <v>123617498</v>
       </c>
       <c r="B42" t="n">
-        <v>92832</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552105</v>
+        <v>552204</v>
       </c>
       <c r="R42" t="n">
-        <v>6992474</v>
+        <v>6992680</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5016,12 +4721,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5036,64 +4741,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128935572</v>
+        <v>123617499</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>552170</v>
+        <v>552214</v>
       </c>
       <c r="R43" t="n">
-        <v>6992588</v>
+        <v>6992683</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5117,12 +4818,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,22 +4838,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128935580</v>
+        <v>123617503</v>
       </c>
       <c r="B44" t="n">
-        <v>92863</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5160,41 +4861,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>232140</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
         <v>552203</v>
       </c>
       <c r="R44" t="n">
-        <v>6992734</v>
+        <v>6992653</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5218,12 +4915,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5238,22 +4935,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128935566</v>
+        <v>123617504</v>
       </c>
       <c r="B45" t="n">
-        <v>88851</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5261,41 +4958,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>816</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552203</v>
+        <v>552209</v>
       </c>
       <c r="R45" t="n">
-        <v>6992734</v>
+        <v>6992635</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5319,12 +5012,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5339,64 +5032,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128935570</v>
+        <v>123617506</v>
       </c>
       <c r="B46" t="n">
-        <v>91473</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552290</v>
+        <v>552200</v>
       </c>
       <c r="R46" t="n">
-        <v>6992648</v>
+        <v>6992631</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5420,12 +5109,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5440,64 +5129,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128935577</v>
+        <v>123617512</v>
       </c>
       <c r="B47" t="n">
-        <v>92844</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>552079</v>
+        <v>552221</v>
       </c>
       <c r="R47" t="n">
-        <v>6992455</v>
+        <v>6992606</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5521,12 +5206,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5541,64 +5226,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128935579</v>
+        <v>123617513</v>
       </c>
       <c r="B48" t="n">
-        <v>92832</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>552082</v>
+        <v>552205</v>
       </c>
       <c r="R48" t="n">
-        <v>6992490</v>
+        <v>6992600</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5622,12 +5303,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5642,64 +5323,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128935578</v>
+        <v>123617514</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>552061</v>
+        <v>552197</v>
       </c>
       <c r="R49" t="n">
-        <v>6992480</v>
+        <v>6992592</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5723,12 +5400,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5743,49 +5420,49 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128935568</v>
+        <v>128935567</v>
       </c>
       <c r="B50" t="n">
-        <v>96970</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5471,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>552214</v>
+        <v>552202</v>
       </c>
       <c r="R50" t="n">
-        <v>6992674</v>
+        <v>6992679</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5859,7 +5536,7 @@
         <v>128935569</v>
       </c>
       <c r="B51" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5957,10 +5634,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128935573</v>
+        <v>97365551</v>
       </c>
       <c r="B52" t="n">
-        <v>90582</v>
+        <v>79085</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5968,41 +5645,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>552099</v>
+        <v>552193</v>
       </c>
       <c r="R52" t="n">
-        <v>6992505</v>
+        <v>6992779</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6026,12 +5699,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6046,22 +5719,26 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128935571</v>
+        <v>123617510</v>
       </c>
       <c r="B53" t="n">
-        <v>91550</v>
+        <v>79085</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6069,41 +5746,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>552188</v>
+        <v>552284</v>
       </c>
       <c r="R53" t="n">
         <v>6992593</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6127,12 +5800,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6147,22 +5820,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128935575</v>
+        <v>97365534</v>
       </c>
       <c r="B54" t="n">
-        <v>92870</v>
+        <v>79917</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6170,41 +5843,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>552093</v>
+        <v>552098</v>
       </c>
       <c r="R54" t="n">
-        <v>6992465</v>
+        <v>6992529</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6228,12 +5897,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6248,64 +5917,64 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128935567</v>
+        <v>123617522</v>
       </c>
       <c r="B55" t="n">
-        <v>98724</v>
+        <v>79917</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sandmon, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>552202</v>
+        <v>552067</v>
       </c>
       <c r="R55" t="n">
-        <v>6992679</v>
+        <v>6992564</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6329,12 +5998,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6349,44 +6018,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128935576</v>
+        <v>128935580</v>
       </c>
       <c r="B56" t="n">
-        <v>92832</v>
+        <v>93228</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6400,10 +6069,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>552087</v>
+        <v>552203</v>
       </c>
       <c r="R56" t="n">
-        <v>6992461</v>
+        <v>6992734</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>

--- a/artfynd/A 8515-2025 artfynd.xlsx
+++ b/artfynd/A 8515-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935568</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365525</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365556</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617524</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935566</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617495</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617511</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935571</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935573</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935570</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365530</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365550</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365555</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2074,6 +2144,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365563</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2171,6 +2246,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617491</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2268,6 +2348,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617492</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2365,6 +2450,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617500</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2462,6 +2552,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617523</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2563,6 +2658,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935574</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2664,6 +2764,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935576</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2765,6 +2870,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935579</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2866,6 +2976,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935577</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617515</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3064,6 +3184,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935575</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3161,6 +3286,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617520</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3262,6 +3392,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365539</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3363,6 +3498,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365538</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3460,6 +3600,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617494</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3557,6 +3702,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617509</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3658,6 +3808,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365544</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3759,6 +3914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365537</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3861,6 +4021,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617518</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3962,6 +4127,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935572</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4063,6 +4233,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365564</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4160,6 +4335,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617521</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4261,6 +4441,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935578</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4362,6 +4547,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365532</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4459,6 +4649,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617493</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4556,6 +4751,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617496</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4653,6 +4853,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617497</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4750,6 +4955,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617498</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4847,6 +5057,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617499</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4944,6 +5159,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617503</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5041,6 +5261,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617504</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5138,6 +5363,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617506</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5235,6 +5465,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617512</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5332,6 +5567,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617513</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5429,6 +5669,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617514</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5530,6 +5775,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935567</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5631,6 +5881,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935569</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5732,6 +5987,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365551</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5829,6 +6089,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617510</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5930,6 +6195,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365534</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6027,6 +6297,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617522</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6128,8 +6403,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935580</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>